--- a/docs/SCOPE_MOSCOW.xlsx
+++ b/docs/SCOPE_MOSCOW.xlsx
@@ -546,7 +546,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Voxistics scope (MoSCoW)</t>
+          <t>walkgrid scope (MoSCoW)</t>
         </is>
       </c>
     </row>
@@ -556,7 +556,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Horizon (edit this): the next playable build -- a world you can build in, decorate and hear, with item logistics decided.</t>
+          <t>Horizon (edit this): the first functional test -- walk a faceted, textured, lit world, hear footsteps with the music, place and remove ground, at 60 fps or better on the owner's PC.</t>
         </is>
       </c>
     </row>
@@ -705,17 +705,17 @@
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>S001</t>
+          <t>W001</t>
         </is>
       </c>
       <c r="B2" s="6" t="inlineStr">
         <is>
-          <t>Engine</t>
+          <t>Process</t>
         </is>
       </c>
       <c r="C2" s="6" t="inlineStr">
         <is>
-          <t>Chunked world, streaming, eviction, regeneration</t>
+          <t>Engine review, prototype outline, foundations</t>
         </is>
       </c>
       <c r="D2" s="6" t="inlineStr">
@@ -728,10 +728,14 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="F2" s="6" t="inlineStr"/>
+      <c r="F2" s="6" t="inlineStr">
+        <is>
+          <t>docs/ENGINE_REVIEW.md, PROTOTYPE_OUTLINE.md, FOUNDATIONS.md</t>
+        </is>
+      </c>
       <c r="G2" s="6" t="inlineStr">
         <is>
-          <t>Part II</t>
+          <t>Foundations</t>
         </is>
       </c>
       <c r="H2" s="6" t="inlineStr">
@@ -743,17 +747,17 @@
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
         <is>
-          <t>S002</t>
+          <t>W002</t>
         </is>
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>Engine</t>
+          <t>Process</t>
         </is>
       </c>
       <c r="C3" s="6" t="inlineStr">
         <is>
-          <t>Save/load: slots, autosave, backups, settings file</t>
+          <t>Plan, approve, build, check; say plainly what wasn't verified</t>
         </is>
       </c>
       <c r="D3" s="6" t="inlineStr">
@@ -763,13 +767,17 @@
       </c>
       <c r="E3" s="6" t="inlineStr">
         <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="F3" s="6" t="inlineStr"/>
+          <t>In progress</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t>Standing rule, never 'done'</t>
+        </is>
+      </c>
       <c r="G3" s="6" t="inlineStr">
         <is>
-          <t>Part VII</t>
+          <t>Foundations 1</t>
         </is>
       </c>
       <c r="H3" s="6" t="inlineStr">
@@ -781,7 +789,7 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>S003</t>
+          <t>W003</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -791,7 +799,7 @@
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Native tests + frame profiler (F3)</t>
+          <t>Carry the Voxistics engine across intact; take only the Voxistics game layer off (M0)</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
@@ -801,17 +809,17 @@
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Every change keeps tests at zero failures</t>
+          <t>Frames before and after must match, minus removed features</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>Parts XVI-XVII</t>
+          <t>Engine review 3</t>
         </is>
       </c>
       <c r="H4" s="6" t="inlineStr">
@@ -823,7 +831,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>S004</t>
+          <t>W004</t>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
@@ -833,7 +841,7 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>Lagless rule: cost scales with what's on screen or changing</t>
+          <t>Lots of action without lag: cost scales with what's on screen or changing</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
@@ -853,7 +861,7 @@
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>CLAUDE.md</t>
+          <t>Foundations 4</t>
         </is>
       </c>
       <c r="H5" s="6" t="inlineStr">
@@ -865,7 +873,7 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>S005</t>
+          <t>W005</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
@@ -875,12 +883,12 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Release-build performance check on the owner's PC</t>
+          <t>60 fps floor; higher where the machine allows, with no jitter (interpolated rendering)</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>Should</t>
+          <t>Must</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
@@ -890,34 +898,34 @@
       </c>
       <c r="F6" s="6" t="inlineStr">
         <is>
-          <t>The Ctrl+F3 report tool exists (perf_report.txt); running the check awaits the owner</t>
+          <t>Checklist T12, T13</t>
         </is>
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>Part XVI</t>
+          <t>Outline D10</t>
         </is>
       </c>
       <c r="H6" s="6" t="inlineStr">
         <is>
-          <t>Claude (proposed)</t>
+          <t>Owner</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>S006</t>
+          <t>W006</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>Blocks &amp; art</t>
+          <t>Engine</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>Block registry, shapes, 32 px materials with normal/shine/glow maps</t>
+          <t>Working name walkgrid: project, window, save folder</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
@@ -927,17 +935,17 @@
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>32 px chosen by owner</t>
+          <t>M0</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>4.3, 4.13</t>
+          <t>Outline D11</t>
         </is>
       </c>
       <c r="H7" s="6" t="inlineStr">
@@ -949,17 +957,17 @@
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>S007</t>
+          <t>W007</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>Blocks &amp; art</t>
+          <t>Engine</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Natural, dark, genesis and custodian material sets</t>
+          <t>Layer rule plus tools/check_layers.sh</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
@@ -969,13 +977,17 @@
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="F8" s="6" t="inlineStr"/>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>Approved with the foundations</t>
+        </is>
+      </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>Foundations 2</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
@@ -987,17 +999,17 @@
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>S008</t>
+          <t>W008</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>Blocks &amp; art</t>
+          <t>Engine</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>Plant cards</t>
+          <t>Thread model: main thread owns world and graphics; 2 job threads build from copies; version stamps</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
@@ -1007,13 +1019,17 @@
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="F9" s="6" t="inlineStr"/>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>Approved with the foundations</t>
+        </is>
+      </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>4.14</t>
+          <t>Foundations 3</t>
         </is>
       </c>
       <c r="H9" s="6" t="inlineStr">
@@ -1025,17 +1041,17 @@
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>S009</t>
+          <t>W009</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>Blocks &amp; art</t>
+          <t>Engine</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Faceted props + dwelling/industry pieces (40 blocks)</t>
+          <t>Fresh walkgrid save format v1 (no Voxistics loaders)</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
@@ -1045,17 +1061,17 @@
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="F10" s="6" t="inlineStr">
         <is>
-          <t>In the library only, not world gen yet</t>
+          <t>Approved with the foundations</t>
         </is>
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>4.15</t>
+          <t>Foundations 5</t>
         </is>
       </c>
       <c r="H10" s="6" t="inlineStr">
@@ -1067,17 +1083,17 @@
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>S010</t>
+          <t>W010</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>Blocks &amp; art</t>
+          <t>Engine</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>Try the library out in the landscape</t>
+          <t>Camera-relative rendering (no jitter far from the start)</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
@@ -1087,17 +1103,17 @@
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
-          <t>Owner play-test; decides names and what stays</t>
+          <t>Approved with the foundations</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>4.15</t>
+          <t>Foundations 4.2</t>
         </is>
       </c>
       <c r="H11" s="6" t="inlineStr">
@@ -1109,22 +1125,22 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>S011</t>
+          <t>W011</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>Blocks &amp; art</t>
+          <t>Engine</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Name pass over all blocks</t>
+          <t>Budgets per frame shown in F3</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>Should</t>
+          <t>Must</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
@@ -1134,12 +1150,12 @@
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
-          <t>After the landscape try-out</t>
+          <t>Numbers are conservative assumptions; tuned only from reports the owner chooses to share</t>
         </is>
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>Part VIII</t>
+          <t>Foundations 4</t>
         </is>
       </c>
       <c r="H12" s="6" t="inlineStr">
@@ -1151,37 +1167,37 @@
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>S012</t>
+          <t>W012</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>Blocks &amp; art</t>
+          <t>World</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>Landmark shapes: canopy cap, coil stalk</t>
+          <t>Faceted surface over the existing grid (option A), not cubes, not blobs</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>Could</t>
+          <t>Must</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>Glowcap, moss canopy, fern coil, sprout coil in the library</t>
+          <t>One-block cells; detail is visual only</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>4.15</t>
+          <t>Outline 3</t>
         </is>
       </c>
       <c r="H13" s="6" t="inlineStr">
@@ -1193,37 +1209,37 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>S013</t>
+          <t>W013</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>Blocks &amp; art</t>
+          <t>World</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Parked decorative set: stained glass, porcelain floral, rune shrine</t>
+          <t>Smaller ground triangles near the player without hurting performance</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>Won't</t>
+          <t>Must</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>Parked</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
-          <t>Dev pile; not this horizon</t>
+          <t>Subdivide only where it shows; set from preview-tool counts</t>
         </is>
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>Part XX</t>
+          <t>Foundations 4.1</t>
         </is>
       </c>
       <c r="H14" s="6" t="inlineStr">
@@ -1235,7 +1251,7 @@
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>S014</t>
+          <t>W014</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
@@ -1245,12 +1261,12 @@
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>World / biome generation using the library blocks and props</t>
+          <t>Walk around: walk, sprint, crouch, jump, slide on facets</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>Should</t>
+          <t>Must</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
@@ -1260,12 +1276,12 @@
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>'Coming in the pipeline'; not started</t>
+          <t>Checklist T6</t>
         </is>
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>Part II</t>
+          <t>Outline 5</t>
         </is>
       </c>
       <c r="H15" s="6" t="inlineStr">
@@ -1277,17 +1293,17 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>S015</t>
+          <t>W015</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>Rendering</t>
+          <t>World</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Lighting, shadows, atmosphere, clouds, bloom, see-through blocks, glow light</t>
+          <t>Place and remove ground, one cell at a time, where the crosshair points</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
@@ -1297,13 +1313,17 @@
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="F16" s="6" t="inlineStr"/>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>Checklist T8</t>
+        </is>
+      </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>4.8-4.12</t>
+          <t>Outline 5</t>
         </is>
       </c>
       <c r="H16" s="6" t="inlineStr">
@@ -1315,59 +1335,59 @@
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>S016</t>
+          <t>W016</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>Rendering</t>
+          <t>World</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>Soft filtering / colour bleed / large-scale variation comparison</t>
+          <t>Seeded test landscape: meadow, dirt, stone, sand regions</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>Could</t>
+          <t>Should</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>Owner picked D; colour bleed dropped after the playtest (halo). Variation + distance filtering kept (4.16)</t>
+          <t>Replaces the flat plain; versioned generator</t>
         </is>
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>Part XX</t>
+          <t>Outline 3</t>
         </is>
       </c>
       <c r="H17" s="6" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>Claude (proposed)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>S017</t>
+          <t>W017</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>Gameplay</t>
+          <t>Looks</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Movement: sprint, crouch, power slide</t>
+          <t>Textures and lighting carried over (sun, shadows, sky, fog, AO, bloom, glow)</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
@@ -1377,13 +1397,17 @@
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="F18" s="6" t="inlineStr"/>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>Checklist T4</t>
+        </is>
+      </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>Outline D4</t>
         </is>
       </c>
       <c r="H18" s="6" t="inlineStr">
@@ -1395,17 +1419,17 @@
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>S018</t>
+          <t>W018</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>Gameplay</t>
+          <t>Looks</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>Block library + 10-slot hotbar</t>
+          <t>Smooth-filtered textures</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
@@ -1415,13 +1439,13 @@
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="F19" s="6" t="inlineStr"/>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="n"/>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>Outline D8</t>
         </is>
       </c>
       <c r="H19" s="6" t="inlineStr">
@@ -1433,17 +1457,17 @@
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>S019</t>
+          <t>W019</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>Gameplay</t>
+          <t>Looks</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Debug time control (F8, [ ])</t>
+          <t>Natural blending between materials (height-based)</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
@@ -1453,13 +1477,17 @@
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="F20" s="6" t="inlineStr"/>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>Checklist T3</t>
+        </is>
+      </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>Part XV</t>
+          <t>Outline 4</t>
         </is>
       </c>
       <c r="H20" s="6" t="inlineStr">
@@ -1471,64 +1499,64 @@
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>S020</t>
+          <t>W020</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>Industry</t>
+          <t>Looks</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>Item logistics: pulse through pipes</t>
+          <t>Sky light: pits, overhangs and hollows go dark</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>Must</t>
+          <t>Should</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="F21" s="6" t="inlineStr">
         <is>
-          <t>Built: harvester at a constant rate (faster under The Line); plain/clockwise/anticlockwise pipes give pulse spin; networks share out to stores (unlimited) and the machine; open ends fire straight, facing mouths catch; store view with bead heaps. Open: what harvesters draw from, what pulse becomes.</t>
+          <t>Checklist T5</t>
         </is>
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>Part VI</t>
+          <t>Outline D4</t>
         </is>
       </c>
       <c r="H21" s="6" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>Claude (proposed)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>S021</t>
+          <t>W021</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>Industry</t>
+          <t>Sound</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>First working machine (the placeholder becomes real)</t>
+          <t>Day-cycle music as in Voxistics</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>Should</t>
+          <t>Must</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
@@ -1538,54 +1566,54 @@
       </c>
       <c r="F22" s="6" t="inlineStr">
         <is>
-          <t>Core of the factory game. Logistics decided (pulse); waits on what pulse becomes / how it is burned</t>
+          <t>Checklist T10</t>
         </is>
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>Part VI</t>
+          <t>Outline D2</t>
         </is>
       </c>
       <c r="H22" s="6" t="inlineStr">
         <is>
-          <t>Claude (proposed)</t>
+          <t>Owner</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>S022</t>
+          <t>W022</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>Industry</t>
+          <t>Sound</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>Byproducts and land health (industry safe when well run)</t>
+          <t>Footsteps on the beat, by gait and ground material</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>Won't</t>
+          <t>Must</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>Parked</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
         <is>
-          <t>Dev pile; core direction but not this horizon</t>
+          <t>Checklist T7</t>
         </is>
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>Part XX</t>
+          <t>Outline 5</t>
         </is>
       </c>
       <c r="H23" s="6" t="inlineStr">
@@ -1597,22 +1625,22 @@
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>S023</t>
+          <t>W023</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>Industry</t>
+          <t>Sound</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>Essence as a transmutation economy</t>
+          <t>Reactive sound effects that don't interfere with the music</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>Could</t>
+          <t>Must</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
@@ -1622,96 +1650,92 @@
       </c>
       <c r="F24" s="6" t="inlineStr">
         <is>
-          <t>Candidate direction only</t>
+          <t>Checklist T9</t>
         </is>
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>Part XIX</t>
+          <t>Outline D3</t>
         </is>
       </c>
       <c r="H24" s="6" t="inlineStr">
         <is>
-          <t>Claude (proposed)</t>
+          <t>Owner</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>S024</t>
+          <t>W024</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>Threat</t>
+          <t>Sound</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>Ooze rifts born of neglect</t>
+          <t>Effects on their own thread, with a voice cap</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>Won't</t>
+          <t>Should</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>Parked</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="F25" s="6" t="inlineStr">
         <is>
-          <t>Dev pile</t>
+          <t>So busy moments never click or cut out</t>
         </is>
       </c>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>Part XX</t>
+          <t>Outline D3</t>
         </is>
       </c>
       <c r="H25" s="6" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>Claude (proposed)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>S025</t>
+          <t>W025</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>Simulation</t>
+          <t>Controls</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>Fluids</t>
+          <t>First person only</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>Won't</t>
+          <t>Must</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>Parked</t>
-        </is>
-      </c>
-      <c r="F26" s="6" t="inlineStr">
-        <is>
-          <t>Dev pile; heavy</t>
-        </is>
-      </c>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="F26" s="6" t="n"/>
       <c r="G26" s="6" t="inlineStr">
         <is>
-          <t>Part XX</t>
+          <t>Outline D9</t>
         </is>
       </c>
       <c r="H26" s="6" t="inlineStr">
@@ -1723,327 +1747,327 @@
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>S026</t>
+          <t>W026</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>Simulation</t>
+          <t>Controls</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>Vapours and gases</t>
+          <t>Raw mouse input</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>Won't</t>
+          <t>Should</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>Parked</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="F27" s="6" t="inlineStr">
         <is>
-          <t>Dev pile; heavy</t>
+          <t>M0</t>
         </is>
       </c>
       <c r="G27" s="6" t="inlineStr">
         <is>
-          <t>Part XX</t>
+          <t>Engine review 2.7</t>
         </is>
       </c>
       <c r="H27" s="6" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>Claude (proposed)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>S027</t>
+          <t>W027</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>Simulation</t>
+          <t>Controls</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>Plants drop when their support is removed</t>
+          <t>Hotbar and material library carried over</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>Won't</t>
+          <t>Should</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
-          <t>Parked</t>
-        </is>
-      </c>
-      <c r="F28" s="6" t="inlineStr">
-        <is>
-          <t>Dev pile</t>
-        </is>
-      </c>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="F28" s="6" t="n"/>
       <c r="G28" s="6" t="inlineStr">
         <is>
-          <t>Part XX</t>
+          <t>Outline 7</t>
         </is>
       </c>
       <c r="H28" s="6" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>Claude (proposed)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>S028</t>
+          <t>W028</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>Audio</t>
+          <t>Menus</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>Day-cycle music (one clock)</t>
+          <t>Title, slots, pause, options (look, graphics, display, audio, keys, accessibility), saves</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>Must</t>
+          <t>Should</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="F29" s="6" t="inlineStr"/>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="F29" s="6" t="inlineStr">
+        <is>
+          <t>Carried over; checklist T11</t>
+        </is>
+      </c>
       <c r="G29" s="6" t="inlineStr">
         <is>
-          <t>Part XIV</t>
+          <t>Outline 7</t>
         </is>
       </c>
       <c r="H29" s="6" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>Claude (proposed)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>S029</t>
+          <t>W029</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>Audio</t>
+          <t>Debug &amp; checks</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>World sound palette + three soundscape axes</t>
+          <t>Screenshot key</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>Must</t>
+          <t>Should</t>
         </is>
       </c>
       <c r="E30" s="6" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="F30" s="6" t="inlineStr">
         <is>
-          <t>Owner finds it plain; develop later</t>
+          <t>M0; for comparing builds</t>
         </is>
       </c>
       <c r="G30" s="6" t="inlineStr">
         <is>
-          <t>10.4</t>
+          <t>Foundations 7</t>
         </is>
       </c>
       <c r="H30" s="6" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>Claude (proposed)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>S030</t>
+          <t>W030</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>Audio</t>
+          <t>Debug &amp; checks</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>Develop the palette's character further</t>
+          <t>MinGW cross-compile and shader check set up here</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>Could</t>
+          <t>Should</t>
         </is>
       </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="F31" s="6" t="inlineStr">
         <is>
-          <t>When the game's direction is clearer</t>
+          <t>Tools being installed</t>
         </is>
       </c>
       <c r="G31" s="6" t="inlineStr">
         <is>
-          <t>10.4</t>
+          <t>Foundations 7</t>
         </is>
       </c>
       <c r="H31" s="6" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>Claude (proposed)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>S031</t>
+          <t>W031</t>
         </is>
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>Audio</t>
+          <t>Debug &amp; checks</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>Machine sounds react to the placeholder machine</t>
+          <t>CPU still-image preview of faceted ground (with triangle counts)</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>Must</t>
+          <t>Should</t>
         </is>
       </c>
       <c r="E32" s="6" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="F32" s="6" t="inlineStr">
         <is>
-          <t>Online on placing; hum and rhythm near machines</t>
+          <t>M1's first deliverable</t>
         </is>
       </c>
       <c r="G32" s="6" t="inlineStr">
         <is>
-          <t>10.4</t>
+          <t>Foundations 4.1</t>
         </is>
       </c>
       <c r="H32" s="6" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>Claude (proposed)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>S032</t>
+          <t>W032</t>
         </is>
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>Audio</t>
+          <t>Debug &amp; checks</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>Positional (stereo) sound</t>
+          <t>Release performance check on the owner's PC (Ctrl+F3 report)</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>Could</t>
+          <t>Should</t>
         </is>
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="F33" s="6" t="inlineStr">
         <is>
-          <t>Owner: go ahead. Placed sounds pan, ping-pong echo, Mono audio toggle</t>
+          <t>Awaits the owner at each milestone</t>
         </is>
       </c>
       <c r="G33" s="6" t="inlineStr">
         <is>
-          <t>10.3</t>
+          <t>Foundations 7</t>
         </is>
       </c>
       <c r="H33" s="6" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>Claude (proposed)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>S033</t>
+          <t>W033</t>
         </is>
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>Audio</t>
+          <t>Docs</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>Sounds waiting on systems: mending, rift closed, rift omens</t>
+          <t>New CLAUDE.md, DESIGN.md and DECISIONS.md; Voxistics docs archived</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>Won't</t>
+          <t>Should</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr">
         <is>
-          <t>Parked</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="F34" s="6" t="inlineStr">
         <is>
-          <t>Built and tested; nothing triggers them yet</t>
+          <t>M0</t>
         </is>
       </c>
       <c r="G34" s="6" t="inlineStr">
         <is>
-          <t>10.4</t>
+          <t>Foundations 6</t>
         </is>
       </c>
       <c r="H34" s="6" t="inlineStr">
@@ -2055,159 +2079,159 @@
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>S034</t>
+          <t>W034</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>The Line</t>
+          <t>Docs</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>The Line prototype: travelling pivot, clockwise spin, time expression</t>
+          <t>Split game.cpp into input, menus, hud</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>Must</t>
+          <t>Should</t>
         </is>
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="F35" s="6" t="inlineStr">
         <is>
-          <t>Playtest fixes: pivot now lands on the spot you actually spend time in x and z (16-block cells remembering where their time was spent; 30-min half-life). Expression (owner's pick): the visible sky races ahead near the line and runs slow after you leave; sun and light keep the real clock; wobble kept faint.</t>
+          <t>M0</t>
         </is>
       </c>
       <c r="G35" s="6" t="inlineStr">
         <is>
-          <t>Part XVIII</t>
+          <t>Engine review 2.7</t>
         </is>
       </c>
       <c r="H35" s="6" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>Claude (proposed)</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t>S035</t>
+          <t>W035</t>
         </is>
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>The Line</t>
+          <t>Later</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>Hide the debug marker once the sky effect is signed off</t>
+          <t>Third person and an animated player model</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>Should</t>
+          <t>Won't</t>
         </is>
       </c>
       <c r="E36" s="6" t="inlineStr">
         <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="F36" s="6" t="inlineStr"/>
+          <t>Parked</t>
+        </is>
+      </c>
+      <c r="F36" s="6" t="inlineStr">
+        <is>
+          <t>If wanted</t>
+        </is>
+      </c>
       <c r="G36" s="6" t="inlineStr">
         <is>
-          <t>Part XVIII</t>
+          <t>Outline D9</t>
         </is>
       </c>
       <c r="H36" s="6" t="inlineStr">
         <is>
-          <t>Claude (proposed)</t>
+          <t>Owner</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>S036</t>
+          <t>W036</t>
         </is>
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>The Line</t>
+          <t>Later</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>Player structures as extra pivot sources</t>
+          <t>Death metal music</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>Could</t>
+          <t>Won't</t>
         </is>
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Parked</t>
         </is>
       </c>
       <c r="F37" s="6" t="inlineStr">
         <is>
-          <t>Owner expected the essence attractor to do this; today it doesn't (it only draws from convergence zones). Owner to decide whether attractors should pull The Line's pivot.</t>
+          <t>Real instruments are hard to emulate</t>
         </is>
       </c>
       <c r="G37" s="6" t="inlineStr">
         <is>
-          <t>Part XVIII</t>
+          <t>Outline D2</t>
         </is>
       </c>
       <c r="H37" s="6" t="inlineStr">
         <is>
-          <t>Claude (proposed)</t>
+          <t>Owner</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>S038</t>
+          <t>W037</t>
         </is>
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>Standing rules</t>
+          <t>Later</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>Nothing anyone owns: no brands, currencies, crypto, borrowed art or names</t>
+          <t>Action systems: enemies, projectiles, particles, with budgets</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>Must</t>
+          <t>Won't</t>
         </is>
       </c>
       <c r="E38" s="6" t="inlineStr">
         <is>
-          <t>In progress</t>
-        </is>
-      </c>
-      <c r="F38" s="6" t="inlineStr">
-        <is>
-          <t>Standing rule</t>
-        </is>
-      </c>
+          <t>Parked</t>
+        </is>
+      </c>
+      <c r="F38" s="6" t="n"/>
       <c r="G38" s="6" t="inlineStr">
         <is>
-          <t>Part VIII</t>
+          <t>Outline 2</t>
         </is>
       </c>
       <c r="H38" s="6" t="inlineStr">
@@ -2219,37 +2243,33 @@
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>S039</t>
+          <t>W038</t>
         </is>
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>Standing rules</t>
+          <t>Later</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>Photosensitivity: nothing flashes more than 3 times a second</t>
+          <t>Real terrain generator with caves</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>Must</t>
+          <t>Won't</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>In progress</t>
-        </is>
-      </c>
-      <c r="F39" s="6" t="inlineStr">
-        <is>
-          <t>Standing rule</t>
-        </is>
-      </c>
+          <t>Parked</t>
+        </is>
+      </c>
+      <c r="F39" s="6" t="n"/>
       <c r="G39" s="6" t="inlineStr">
         <is>
-          <t>Part XI</t>
+          <t>Outline 2</t>
         </is>
       </c>
       <c r="H39" s="6" t="inlineStr">
@@ -2261,37 +2281,37 @@
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t>S040</t>
+          <t>W039</t>
         </is>
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>Audio</t>
+          <t>Later</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>Vocal ad-libs and footfalls</t>
+          <t>Unsupported ground falls (Voxistics gravity)</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>Must</t>
+          <t>Won't</t>
         </is>
       </c>
       <c r="E40" s="6" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Parked</t>
         </is>
       </c>
       <c r="F40" s="6" t="inlineStr">
         <is>
-          <t>Owner: keep</t>
+          <t>Revisit after the first test</t>
         </is>
       </c>
       <c r="G40" s="6" t="inlineStr">
         <is>
-          <t>10.4</t>
+          <t>Outline 7</t>
         </is>
       </c>
       <c r="H40" s="6" t="inlineStr">
@@ -2303,17 +2323,17 @@
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>S041</t>
+          <t>W040</t>
         </is>
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>Audio</t>
+          <t>Later</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>'Unveil' cue on first placement of a block type</t>
+          <t>Covered grass dies back to dirt</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
@@ -2328,12 +2348,12 @@
       </c>
       <c r="F41" s="6" t="inlineStr">
         <is>
-          <t>Owner: nixed; the recipe stays unused</t>
+          <t>Revisit after the first test</t>
         </is>
       </c>
       <c r="G41" s="6" t="inlineStr">
         <is>
-          <t>10.4</t>
+          <t>Outline 7</t>
         </is>
       </c>
       <c r="H41" s="6" t="inlineStr">
@@ -2345,37 +2365,37 @@
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t>S042</t>
+          <t>W041</t>
         </is>
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>Audio</t>
+          <t>Later</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>Footsteps on the beat, by gait and ground hardness</t>
+          <t>Plants that turn to face you</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>Must</t>
+          <t>Won't</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Parked</t>
         </is>
       </c>
       <c r="F42" s="6" t="inlineStr">
         <is>
-          <t>Crouch/walk/sprint; soft scuffs, hard knocks in key</t>
+          <t>Revisit after the first test</t>
         </is>
       </c>
       <c r="G42" s="6" t="inlineStr">
         <is>
-          <t>10.4</t>
+          <t>Outline 7</t>
         </is>
       </c>
       <c r="H42" s="6" t="inlineStr">
@@ -2387,964 +2407,320 @@
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>S043</t>
+          <t>W042</t>
         </is>
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>World</t>
+          <t>Later</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>Default plain as a fractal patchwork of three ground materials</t>
+          <t>See-through materials (glass, ice, water)</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>Must</t>
+          <t>Won't</t>
         </is>
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="F43" s="6" t="inlineStr">
-        <is>
-          <t>Grass / sand / pebbles by feel underfoot; flat v2; materials swappable</t>
-        </is>
-      </c>
+          <t>Parked</t>
+        </is>
+      </c>
+      <c r="F43" s="6" t="n"/>
       <c r="G43" s="6" t="inlineStr">
         <is>
-          <t>Part II</t>
+          <t>Outline 7</t>
         </is>
       </c>
       <c r="H43" s="6" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>Claude (proposed)</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
         <is>
-          <t>S044</t>
+          <t>W043</t>
         </is>
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>UI</t>
+          <t>Later</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>Buttons that look and feel pressable (mechanical press cue)</t>
+          <t>Colour-vision modes; first-steps tutorial</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr">
         <is>
-          <t>Must</t>
+          <t>Won't</t>
         </is>
       </c>
       <c r="E44" s="6" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Parked</t>
         </is>
       </c>
       <c r="F44" s="6" t="inlineStr">
         <is>
-          <t>Keys act on release; sliders are beads on a string</t>
+          <t>Served Voxistics features</t>
         </is>
       </c>
       <c r="G44" s="6" t="inlineStr">
         <is>
-          <t>Part XII</t>
+          <t>Outline 7</t>
         </is>
       </c>
       <c r="H44" s="6" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>Claude (proposed)</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>S045</t>
+          <t>W044</t>
         </is>
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>Standing rules</t>
+          <t>Later</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>Privacy: no telemetry, crash reporting or hardware reading; target a modest old Windows PC</t>
+          <t>Gamepad support</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>Must</t>
+          <t>Won't</t>
         </is>
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>In progress</t>
-        </is>
-      </c>
-      <c r="F45" s="6" t="inlineStr">
-        <is>
-          <t>Standing rule</t>
-        </is>
-      </c>
+          <t>Parked</t>
+        </is>
+      </c>
+      <c r="F45" s="6" t="n"/>
       <c r="G45" s="6" t="inlineStr">
         <is>
-          <t>CLAUDE.md</t>
+          <t>Engine review 2.7</t>
         </is>
       </c>
       <c r="H45" s="6" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>Claude (proposed)</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="6" t="inlineStr">
-        <is>
-          <t>S046</t>
-        </is>
-      </c>
-      <c r="B46" s="6" t="inlineStr">
-        <is>
-          <t>Crafting</t>
-        </is>
-      </c>
-      <c r="C46" s="6" t="inlineStr">
-        <is>
-          <t>Crafting system brainstorm: gathering, representation, uses, advancement from the natural surroundings</t>
-        </is>
-      </c>
-      <c r="D46" s="6" t="inlineStr">
-        <is>
-          <t>Should</t>
-        </is>
-      </c>
-      <c r="E46" s="6" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="F46" s="6" t="inlineStr">
-        <is>
-          <t>After the playtest. Seed: microbes/germs gathered as essence, coloured/'flavoured' by the source's biological makeup. Owner to confirm priority.</t>
-        </is>
-      </c>
-      <c r="G46" s="6" t="inlineStr">
-        <is>
-          <t>Part XX</t>
-        </is>
-      </c>
-      <c r="H46" s="6" t="inlineStr">
-        <is>
-          <t>Owner</t>
-        </is>
-      </c>
+      <c r="A46" s="6" t="n"/>
+      <c r="B46" s="6" t="n"/>
+      <c r="C46" s="6" t="n"/>
+      <c r="D46" s="6" t="n"/>
+      <c r="E46" s="6" t="n"/>
+      <c r="F46" s="6" t="n"/>
+      <c r="G46" s="6" t="n"/>
+      <c r="H46" s="6" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" s="6" t="inlineStr">
-        <is>
-          <t>S047</t>
-        </is>
-      </c>
-      <c r="B47" s="6" t="inlineStr">
-        <is>
-          <t>Playtest fixes</t>
-        </is>
-      </c>
-      <c r="C47" s="6" t="inlineStr">
-        <is>
-          <t>Footsteps louder; fog haze + distance filtering; midday hitch (music slices, sliced shadow redraw)</t>
-        </is>
-      </c>
-      <c r="D47" s="6" t="inlineStr">
-        <is>
-          <t>Must</t>
-        </is>
-      </c>
-      <c r="E47" s="6" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="F47" s="6" t="inlineStr">
-        <is>
-          <t>From the first playtest on the owner's rig</t>
-        </is>
-      </c>
-      <c r="G47" s="6" t="inlineStr">
-        <is>
-          <t>4.8, 4.16, 14.7</t>
-        </is>
-      </c>
-      <c r="H47" s="6" t="inlineStr">
-        <is>
-          <t>Owner</t>
-        </is>
-      </c>
+      <c r="A47" s="6" t="n"/>
+      <c r="B47" s="6" t="n"/>
+      <c r="C47" s="6" t="n"/>
+      <c r="D47" s="6" t="n"/>
+      <c r="E47" s="6" t="n"/>
+      <c r="F47" s="6" t="n"/>
+      <c r="G47" s="6" t="n"/>
+      <c r="H47" s="6" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" s="6" t="inlineStr">
-        <is>
-          <t>S048</t>
-        </is>
-      </c>
-      <c r="B48" s="6" t="inlineStr">
-        <is>
-          <t>Gameplay</t>
-        </is>
-      </c>
-      <c r="C48" s="6" t="inlineStr">
-        <is>
-          <t>Forgiving power-slide timing; faster sprint (7.5)</t>
-        </is>
-      </c>
-      <c r="D48" s="6" t="inlineStr">
-        <is>
-          <t>Must</t>
-        </is>
-      </c>
-      <c r="E48" s="6" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="F48" s="6" t="inlineStr">
-        <is>
-          <t>Crouch/sprint in either order within 0.3-0.4 s</t>
-        </is>
-      </c>
-      <c r="G48" s="6" t="inlineStr">
-        <is>
-          <t>4.7</t>
-        </is>
-      </c>
-      <c r="H48" s="6" t="inlineStr">
-        <is>
-          <t>Owner</t>
-        </is>
-      </c>
+      <c r="A48" s="6" t="n"/>
+      <c r="B48" s="6" t="n"/>
+      <c r="C48" s="6" t="n"/>
+      <c r="D48" s="6" t="n"/>
+      <c r="E48" s="6" t="n"/>
+      <c r="F48" s="6" t="n"/>
+      <c r="G48" s="6" t="n"/>
+      <c r="H48" s="6" t="n"/>
     </row>
     <row r="49">
-      <c r="A49" s="6" t="inlineStr">
-        <is>
-          <t>S049</t>
-        </is>
-      </c>
-      <c r="B49" s="6" t="inlineStr">
-        <is>
-          <t>Rendering</t>
-        </is>
-      </c>
-      <c r="C49" s="6" t="inlineStr">
-        <is>
-          <t>Frame rate limit 30-200 (default 60) and vsync toggle</t>
-        </is>
-      </c>
-      <c r="D49" s="6" t="inlineStr">
-        <is>
-          <t>Must</t>
-        </is>
-      </c>
-      <c r="E49" s="6" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="F49" s="6" t="inlineStr">
-        <is>
-          <t>Graphics settings</t>
-        </is>
-      </c>
-      <c r="G49" s="6" t="inlineStr">
-        <is>
-          <t>12.y</t>
-        </is>
-      </c>
-      <c r="H49" s="6" t="inlineStr">
-        <is>
-          <t>Owner</t>
-        </is>
-      </c>
+      <c r="A49" s="6" t="n"/>
+      <c r="B49" s="6" t="n"/>
+      <c r="C49" s="6" t="n"/>
+      <c r="D49" s="6" t="n"/>
+      <c r="E49" s="6" t="n"/>
+      <c r="F49" s="6" t="n"/>
+      <c r="G49" s="6" t="n"/>
+      <c r="H49" s="6" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="6" t="inlineStr">
-        <is>
-          <t>S050</t>
-        </is>
-      </c>
-      <c r="B50" s="6" t="inlineStr">
-        <is>
-          <t>Gameplay</t>
-        </is>
-      </c>
-      <c r="C50" s="6" t="inlineStr">
-        <is>
-          <t>Breaking blocks: how it is done, and with what tools (if any)</t>
-        </is>
-      </c>
-      <c r="D50" s="6" t="inlineStr">
-        <is>
-          <t>Could</t>
-        </is>
-      </c>
-      <c r="E50" s="6" t="inlineStr">
-        <is>
-          <t>Parked</t>
-        </is>
-      </c>
-      <c r="F50" s="6" t="inlineStr">
-        <is>
-          <t>Owner: comes later, once we decide what tools there are. Today a click breaks a block instantly. Priority is the owner's to set.</t>
-        </is>
-      </c>
-      <c r="G50" s="6" t="inlineStr">
-        <is>
-          <t>Part XX</t>
-        </is>
-      </c>
-      <c r="H50" s="6" t="inlineStr">
-        <is>
-          <t>Claude (proposed)</t>
-        </is>
-      </c>
+      <c r="A50" s="6" t="n"/>
+      <c r="B50" s="6" t="n"/>
+      <c r="C50" s="6" t="n"/>
+      <c r="D50" s="6" t="n"/>
+      <c r="E50" s="6" t="n"/>
+      <c r="F50" s="6" t="n"/>
+      <c r="G50" s="6" t="n"/>
+      <c r="H50" s="6" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="6" t="inlineStr">
-        <is>
-          <t>S051</t>
-        </is>
-      </c>
-      <c r="B51" s="6" t="inlineStr">
-        <is>
-          <t>Rendering</t>
-        </is>
-      </c>
-      <c r="C51" s="6" t="inlineStr">
-        <is>
-          <t>Pre-generated fracture: a broken block splits into pieces that tumble and settle</t>
-        </is>
-      </c>
-      <c r="D51" s="6" t="inlineStr">
-        <is>
-          <t>Could</t>
-        </is>
-      </c>
-      <c r="E51" s="6" t="inlineStr">
-        <is>
-          <t>Parked</t>
-        </is>
-      </c>
-      <c r="F51" s="6" t="inlineStr">
-        <is>
-          <t>Owner's idea, for with S050. Cheap by design: fracture patterns baked once per shape (a handful of variants), a few short-lived pieces per break, no per-block data. Nothing flashes.</t>
-        </is>
-      </c>
-      <c r="G51" s="6" t="inlineStr">
-        <is>
-          <t>Part XX</t>
-        </is>
-      </c>
-      <c r="H51" s="6" t="inlineStr">
-        <is>
-          <t>Claude (proposed)</t>
-        </is>
-      </c>
+      <c r="A51" s="6" t="n"/>
+      <c r="B51" s="6" t="n"/>
+      <c r="C51" s="6" t="n"/>
+      <c r="D51" s="6" t="n"/>
+      <c r="E51" s="6" t="n"/>
+      <c r="F51" s="6" t="n"/>
+      <c r="G51" s="6" t="n"/>
+      <c r="H51" s="6" t="n"/>
     </row>
     <row r="52">
-      <c r="A52" s="6" t="inlineStr">
-        <is>
-          <t>S052</t>
-        </is>
-      </c>
-      <c r="B52" s="6" t="inlineStr">
-        <is>
-          <t>UI</t>
-        </is>
-      </c>
-      <c r="C52" s="6" t="inlineStr">
-        <is>
-          <t>Translation / language packs</t>
-        </is>
-      </c>
-      <c r="D52" s="6" t="inlineStr">
-        <is>
-          <t>Won't</t>
-        </is>
-      </c>
-      <c r="E52" s="6" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="F52" s="6" t="inlineStr">
-        <is>
-          <t>Owner: not a priority; English only, kept minimal so non-native speakers pick it up through play. Estimate if ever wanted: Latin scripts a few days (string table, accented glyphs); CJK needs a glyph cache.</t>
-        </is>
-      </c>
-      <c r="G52" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H52" s="6" t="inlineStr">
-        <is>
-          <t>Owner</t>
-        </is>
-      </c>
+      <c r="A52" s="6" t="n"/>
+      <c r="B52" s="6" t="n"/>
+      <c r="C52" s="6" t="n"/>
+      <c r="D52" s="6" t="n"/>
+      <c r="E52" s="6" t="n"/>
+      <c r="F52" s="6" t="n"/>
+      <c r="G52" s="6" t="n"/>
+      <c r="H52" s="6" t="n"/>
     </row>
     <row r="53">
-      <c r="A53" s="6" t="inlineStr">
-        <is>
-          <t>S053</t>
-        </is>
-      </c>
-      <c r="B53" s="6" t="inlineStr">
-        <is>
-          <t>Art</t>
-        </is>
-      </c>
-      <c r="C53" s="6" t="inlineStr">
-        <is>
-          <t>A big new batch of library blocks to sort through</t>
-        </is>
-      </c>
-      <c r="D53" s="6" t="inlineStr">
-        <is>
-          <t>Should</t>
-        </is>
-      </c>
-      <c r="E53" s="6" t="inlineStr">
-        <is>
-          <t>In progress</t>
-        </is>
-      </c>
-      <c r="F53" s="6" t="inlineStr">
-        <is>
-          <t>36 trial materials in the library (batch_sept.vtex), four families; waiting on the owner's sort</t>
-        </is>
-      </c>
-      <c r="G53" s="6" t="inlineStr">
-        <is>
-          <t>4.13, 4.15</t>
-        </is>
-      </c>
-      <c r="H53" s="6" t="inlineStr">
-        <is>
-          <t>Owner</t>
-        </is>
-      </c>
+      <c r="A53" s="6" t="n"/>
+      <c r="B53" s="6" t="n"/>
+      <c r="C53" s="6" t="n"/>
+      <c r="D53" s="6" t="n"/>
+      <c r="E53" s="6" t="n"/>
+      <c r="F53" s="6" t="n"/>
+      <c r="G53" s="6" t="n"/>
+      <c r="H53" s="6" t="n"/>
     </row>
     <row r="54">
-      <c r="A54" s="6" t="inlineStr">
-        <is>
-          <t>S054</t>
-        </is>
-      </c>
-      <c r="B54" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="C54" s="6" t="inlineStr">
-        <is>
-          <t>Reviews: music fit; optimisation and architecture; texture library direction</t>
-        </is>
-      </c>
-      <c r="D54" s="6" t="inlineStr">
-        <is>
-          <t>Should</t>
-        </is>
-      </c>
-      <c r="E54" s="6" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="F54" s="6" t="inlineStr">
-        <is>
-          <t>docs/REVIEW_2026-09.md; perf fixes merged, proposals await the owner</t>
-        </is>
-      </c>
-      <c r="G54" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H54" s="6" t="inlineStr">
-        <is>
-          <t>Owner</t>
-        </is>
-      </c>
+      <c r="A54" s="6" t="n"/>
+      <c r="B54" s="6" t="n"/>
+      <c r="C54" s="6" t="n"/>
+      <c r="D54" s="6" t="n"/>
+      <c r="E54" s="6" t="n"/>
+      <c r="F54" s="6" t="n"/>
+      <c r="G54" s="6" t="n"/>
+      <c r="H54" s="6" t="n"/>
     </row>
     <row r="55">
-      <c r="A55" s="6" t="inlineStr">
-        <is>
-          <t>S055</t>
-        </is>
-      </c>
-      <c r="B55" s="6" t="inlineStr">
-        <is>
-          <t>Industry</t>
-        </is>
-      </c>
-      <c r="C55" s="6" t="inlineStr">
-        <is>
-          <t>Pulse spin: three pipe kinds, spin carried and counted</t>
-        </is>
-      </c>
-      <c r="D55" s="6" t="inlineStr">
-        <is>
-          <t>Must</t>
-        </is>
-      </c>
-      <c r="E55" s="6" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="F55" s="6" t="inlineStr">
-        <is>
-          <t>Owner's idea; seen as corkscrew comets in the air and heaps by colour in stores</t>
-        </is>
-      </c>
-      <c r="G55" s="6" t="inlineStr">
-        <is>
-          <t>6.0</t>
-        </is>
-      </c>
-      <c r="H55" s="6" t="inlineStr">
-        <is>
-          <t>Owner</t>
-        </is>
-      </c>
+      <c r="A55" s="6" t="n"/>
+      <c r="B55" s="6" t="n"/>
+      <c r="C55" s="6" t="n"/>
+      <c r="D55" s="6" t="n"/>
+      <c r="E55" s="6" t="n"/>
+      <c r="F55" s="6" t="n"/>
+      <c r="G55" s="6" t="n"/>
+      <c r="H55" s="6" t="n"/>
     </row>
     <row r="56">
-      <c r="A56" s="6" t="inlineStr">
-        <is>
-          <t>S056</t>
-        </is>
-      </c>
-      <c r="B56" s="6" t="inlineStr">
-        <is>
-          <t>World</t>
-        </is>
-      </c>
-      <c r="C56" s="6" t="inlineStr">
-        <is>
-          <t>Fliers: two-winged day-lived creatures that fly low; the line ages them</t>
-        </is>
-      </c>
-      <c r="D56" s="6" t="inlineStr">
-        <is>
-          <t>Should</t>
-        </is>
-      </c>
-      <c r="E56" s="6" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="F56" s="6" t="inlineStr">
-        <is>
-          <t>Owner's idea. Die after one game day or sooner under The Line; death makes grass glow vividly for a while, or grows mold on dirt/wood</t>
-        </is>
-      </c>
-      <c r="G56" s="6" t="inlineStr">
-        <is>
-          <t>Part XXI</t>
-        </is>
-      </c>
-      <c r="H56" s="6" t="inlineStr">
-        <is>
-          <t>Owner</t>
-        </is>
-      </c>
+      <c r="A56" s="6" t="n"/>
+      <c r="B56" s="6" t="n"/>
+      <c r="C56" s="6" t="n"/>
+      <c r="D56" s="6" t="n"/>
+      <c r="E56" s="6" t="n"/>
+      <c r="F56" s="6" t="n"/>
+      <c r="G56" s="6" t="n"/>
+      <c r="H56" s="6" t="n"/>
     </row>
     <row r="57">
-      <c r="A57" s="6" t="inlineStr">
-        <is>
-          <t>S057</t>
-        </is>
-      </c>
-      <c r="B57" s="6" t="inlineStr">
-        <is>
-          <t>World</t>
-        </is>
-      </c>
-      <c r="C57" s="6" t="inlineStr">
-        <is>
-          <t>Mold that sprouts a mushroom after a game day or after rain</t>
-        </is>
-      </c>
-      <c r="D57" s="6" t="inlineStr">
-        <is>
-          <t>Could</t>
-        </is>
-      </c>
-      <c r="E57" s="6" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="F57" s="6" t="inlineStr">
-        <is>
-          <t>Owner's idea; rain needs a weather system (to discuss)</t>
-        </is>
-      </c>
-      <c r="G57" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H57" s="6" t="inlineStr">
-        <is>
-          <t>Claude (proposed)</t>
-        </is>
-      </c>
+      <c r="A57" s="6" t="n"/>
+      <c r="B57" s="6" t="n"/>
+      <c r="C57" s="6" t="n"/>
+      <c r="D57" s="6" t="n"/>
+      <c r="E57" s="6" t="n"/>
+      <c r="F57" s="6" t="n"/>
+      <c r="G57" s="6" t="n"/>
+      <c r="H57" s="6" t="n"/>
     </row>
     <row r="58">
-      <c r="A58" s="6" t="inlineStr">
-        <is>
-          <t>S058</t>
-        </is>
-      </c>
-      <c r="B58" s="6" t="inlineStr">
-        <is>
-          <t>World</t>
-        </is>
-      </c>
-      <c r="C58" s="6" t="inlineStr">
-        <is>
-          <t>Covered grass turns to dirt (not overnight)</t>
-        </is>
-      </c>
-      <c r="D58" s="6" t="inlineStr">
-        <is>
-          <t>Should</t>
-        </is>
-      </c>
-      <c r="E58" s="6" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="F58" s="6" t="inlineStr">
-        <is>
-          <t>Deprived of sky, not of daylight</t>
-        </is>
-      </c>
-      <c r="G58" s="6" t="inlineStr">
-        <is>
-          <t>Part V</t>
-        </is>
-      </c>
-      <c r="H58" s="6" t="inlineStr">
-        <is>
-          <t>Owner</t>
-        </is>
-      </c>
+      <c r="A58" s="6" t="n"/>
+      <c r="B58" s="6" t="n"/>
+      <c r="C58" s="6" t="n"/>
+      <c r="D58" s="6" t="n"/>
+      <c r="E58" s="6" t="n"/>
+      <c r="F58" s="6" t="n"/>
+      <c r="G58" s="6" t="n"/>
+      <c r="H58" s="6" t="n"/>
     </row>
     <row r="59">
-      <c r="A59" s="6" t="inlineStr">
-        <is>
-          <t>S059</t>
-        </is>
-      </c>
-      <c r="B59" s="6" t="inlineStr">
-        <is>
-          <t>World</t>
-        </is>
-      </c>
-      <c r="C59" s="6" t="inlineStr">
-        <is>
-          <t>Weather (rain first)</t>
-        </is>
-      </c>
-      <c r="D59" s="6" t="inlineStr">
-        <is>
-          <t>Could</t>
-        </is>
-      </c>
-      <c r="E59" s="6" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="F59" s="6" t="inlineStr">
-        <is>
-          <t>Owner: yet to discuss</t>
-        </is>
-      </c>
-      <c r="G59" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H59" s="6" t="inlineStr">
-        <is>
-          <t>Claude (proposed)</t>
-        </is>
-      </c>
+      <c r="A59" s="6" t="n"/>
+      <c r="B59" s="6" t="n"/>
+      <c r="C59" s="6" t="n"/>
+      <c r="D59" s="6" t="n"/>
+      <c r="E59" s="6" t="n"/>
+      <c r="F59" s="6" t="n"/>
+      <c r="G59" s="6" t="n"/>
+      <c r="H59" s="6" t="n"/>
     </row>
     <row r="60">
-      <c r="A60" s="6" t="inlineStr">
-        <is>
-          <t>S060</t>
-        </is>
-      </c>
-      <c r="B60" s="6" t="inlineStr">
-        <is>
-          <t>The Line</t>
-        </is>
-      </c>
-      <c r="C60" s="6" t="inlineStr">
-        <is>
-          <t>The Line grows to a plane with the player's power and influence</t>
-        </is>
-      </c>
-      <c r="D60" s="6" t="inlineStr">
-        <is>
-          <t>Won't</t>
-        </is>
-      </c>
-      <c r="E60" s="6" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="F60" s="6" t="inlineStr">
-        <is>
-          <t>Owner: low priority, discuss later</t>
-        </is>
-      </c>
-      <c r="G60" s="6" t="inlineStr">
-        <is>
-          <t>Part XVIII</t>
-        </is>
-      </c>
-      <c r="H60" s="6" t="inlineStr">
-        <is>
-          <t>Owner</t>
-        </is>
-      </c>
+      <c r="A60" s="6" t="n"/>
+      <c r="B60" s="6" t="n"/>
+      <c r="C60" s="6" t="n"/>
+      <c r="D60" s="6" t="n"/>
+      <c r="E60" s="6" t="n"/>
+      <c r="F60" s="6" t="n"/>
+      <c r="G60" s="6" t="n"/>
+      <c r="H60" s="6" t="n"/>
     </row>
     <row r="61">
-      <c r="A61" s="6" t="inlineStr">
-        <is>
-          <t>S061</t>
-        </is>
-      </c>
-      <c r="B61" s="6" t="inlineStr">
-        <is>
-          <t>Industry</t>
-        </is>
-      </c>
-      <c r="C61" s="6" t="inlineStr">
-        <is>
-          <t>Diffuser: spends pulse widening The Line's band (the first loop)</t>
-        </is>
-      </c>
-      <c r="D61" s="6" t="inlineStr">
-        <is>
-          <t>Must</t>
-        </is>
-      </c>
-      <c r="E61" s="6" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="F61" s="6" t="inlineStr">
-        <is>
-          <t>Owner's design: feed per second keeps the band wide; harvesters above/below need it</t>
-        </is>
-      </c>
-      <c r="G61" s="6" t="inlineStr">
-        <is>
-          <t>6.0, XVIII</t>
-        </is>
-      </c>
-      <c r="H61" s="6" t="inlineStr">
-        <is>
-          <t>Owner</t>
-        </is>
-      </c>
+      <c r="A61" s="6" t="n"/>
+      <c r="B61" s="6" t="n"/>
+      <c r="C61" s="6" t="n"/>
+      <c r="D61" s="6" t="n"/>
+      <c r="E61" s="6" t="n"/>
+      <c r="F61" s="6" t="n"/>
+      <c r="G61" s="6" t="n"/>
+      <c r="H61" s="6" t="n"/>
     </row>
     <row r="62">
-      <c r="A62" s="6" t="inlineStr">
-        <is>
-          <t>S062</t>
-        </is>
-      </c>
-      <c r="B62" s="6" t="inlineStr">
-        <is>
-          <t>UI</t>
-        </is>
-      </c>
-      <c r="C62" s="6" t="inlineStr">
-        <is>
-          <t>First-steps tutorial on a new world, skippable</t>
-        </is>
-      </c>
-      <c r="D62" s="6" t="inlineStr">
-        <is>
-          <t>Must</t>
-        </is>
-      </c>
-      <c r="E62" s="6" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="F62" s="6" t="inlineStr">
-        <is>
-          <t>One line at a time, moves on as done; Enter skips</t>
-        </is>
-      </c>
-      <c r="G62" s="6" t="inlineStr">
-        <is>
-          <t>6.0</t>
-        </is>
-      </c>
-      <c r="H62" s="6" t="inlineStr">
-        <is>
-          <t>Owner</t>
-        </is>
-      </c>
+      <c r="A62" s="6" t="n"/>
+      <c r="B62" s="6" t="n"/>
+      <c r="C62" s="6" t="n"/>
+      <c r="D62" s="6" t="n"/>
+      <c r="E62" s="6" t="n"/>
+      <c r="F62" s="6" t="n"/>
+      <c r="G62" s="6" t="n"/>
+      <c r="H62" s="6" t="n"/>
     </row>
     <row r="63">
-      <c r="A63" s="6" t="inlineStr">
-        <is>
-          <t>S063</t>
-        </is>
-      </c>
-      <c r="B63" s="6" t="inlineStr">
-        <is>
-          <t>Gameplay</t>
-        </is>
-      </c>
-      <c r="C63" s="6" t="inlineStr">
-        <is>
-          <t>New world starts with harvester, pipe, chest, diffuser on the hotbar</t>
-        </is>
-      </c>
-      <c r="D63" s="6" t="inlineStr">
-        <is>
-          <t>Must</t>
-        </is>
-      </c>
-      <c r="E63" s="6" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="F63" s="6" t="inlineStr"/>
-      <c r="G63" s="6" t="inlineStr">
-        <is>
-          <t>6.0</t>
-        </is>
-      </c>
-      <c r="H63" s="6" t="inlineStr">
-        <is>
-          <t>Owner</t>
-        </is>
-      </c>
+      <c r="A63" s="6" t="n"/>
+      <c r="B63" s="6" t="n"/>
+      <c r="C63" s="6" t="n"/>
+      <c r="D63" s="6" t="n"/>
+      <c r="E63" s="6" t="n"/>
+      <c r="F63" s="6" t="n"/>
+      <c r="G63" s="6" t="n"/>
+      <c r="H63" s="6" t="n"/>
     </row>
     <row r="64">
-      <c r="A64" s="6" t="inlineStr">
-        <is>
-          <t>S064</t>
-        </is>
-      </c>
-      <c r="B64" s="6" t="inlineStr">
-        <is>
-          <t>Accessibility</t>
-        </is>
-      </c>
-      <c r="C64" s="6" t="inlineStr">
-        <is>
-          <t>Colour-vision modes, one per kind of colour blindness</t>
-        </is>
-      </c>
-      <c r="D64" s="6" t="inlineStr">
-        <is>
-          <t>Should</t>
-        </is>
-      </c>
-      <c r="E64" s="6" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="F64" s="6" t="inlineStr">
-        <is>
-          <t>Accessibility &gt; Colour vision: 5 modes for the pulse colours; tested with dichromat simulations (the big win: no-colour, where blue and red merged)</t>
-        </is>
-      </c>
-      <c r="G64" s="6" t="inlineStr">
-        <is>
-          <t>11.x</t>
-        </is>
-      </c>
-      <c r="H64" s="6" t="inlineStr">
-        <is>
-          <t>Owner</t>
-        </is>
-      </c>
+      <c r="A64" s="6" t="n"/>
+      <c r="B64" s="6" t="n"/>
+      <c r="C64" s="6" t="n"/>
+      <c r="D64" s="6" t="n"/>
+      <c r="E64" s="6" t="n"/>
+      <c r="F64" s="6" t="n"/>
+      <c r="G64" s="6" t="n"/>
+      <c r="H64" s="6" t="n"/>
     </row>
     <row r="65">
-      <c r="A65" s="6" t="inlineStr">
-        <is>
-          <t>S065</t>
-        </is>
-      </c>
-      <c r="B65" s="6" t="inlineStr">
-        <is>
-          <t>Industry</t>
-        </is>
-      </c>
-      <c r="C65" s="6" t="inlineStr">
-        <is>
-          <t>Machines sped up or slowed by time flux</t>
-        </is>
-      </c>
-      <c r="D65" s="6" t="inlineStr">
-        <is>
-          <t>Could</t>
-        </is>
-      </c>
-      <c r="E65" s="6" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="F65" s="6" t="inlineStr">
-        <is>
-          <t>Owner: pipes and pulse in the air stay unaffected; harvesters are the first</t>
-        </is>
-      </c>
-      <c r="G65" s="6" t="inlineStr">
-        <is>
-          <t>6.0</t>
-        </is>
-      </c>
-      <c r="H65" s="6" t="inlineStr">
-        <is>
-          <t>Owner</t>
-        </is>
-      </c>
+      <c r="A65" s="6" t="n"/>
+      <c r="B65" s="6" t="n"/>
+      <c r="C65" s="6" t="n"/>
+      <c r="D65" s="6" t="n"/>
+      <c r="E65" s="6" t="n"/>
+      <c r="F65" s="6" t="n"/>
+      <c r="G65" s="6" t="n"/>
+      <c r="H65" s="6" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="6" t="n"/>

--- a/docs/SCOPE_MOSCOW.xlsx
+++ b/docs/SCOPE_MOSCOW.xlsx
@@ -809,7 +809,7 @@
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
@@ -2523,14 +2523,46 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="6" t="n"/>
-      <c r="B46" s="6" t="n"/>
-      <c r="C46" s="6" t="n"/>
-      <c r="D46" s="6" t="n"/>
-      <c r="E46" s="6" t="n"/>
-      <c r="F46" s="6" t="n"/>
-      <c r="G46" s="6" t="n"/>
-      <c r="H46" s="6" t="n"/>
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t>W045</t>
+        </is>
+      </c>
+      <c r="B46" s="6" t="inlineStr">
+        <is>
+          <t>Engine</t>
+        </is>
+      </c>
+      <c r="C46" s="6" t="inlineStr">
+        <is>
+          <t>Render only what can be seen; preload what may be seen soon</t>
+        </is>
+      </c>
+      <c r="D46" s="6" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="E46" s="6" t="inlineStr">
+        <is>
+          <t>In progress</t>
+        </is>
+      </c>
+      <c r="F46" s="6" t="inlineStr">
+        <is>
+          <t>Frustum culling exists; hidden-chunk skipping and heading-aware loading in M1</t>
+        </is>
+      </c>
+      <c r="G46" s="6" t="inlineStr">
+        <is>
+          <t>Foundations 4.3</t>
+        </is>
+      </c>
+      <c r="H46" s="6" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="6" t="n"/>

--- a/docs/SCOPE_MOSCOW.xlsx
+++ b/docs/SCOPE_MOSCOW.xlsx
@@ -977,12 +977,12 @@
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="F8" s="6" t="inlineStr">
         <is>
-          <t>Approved with the foundations</t>
+          <t>tools/check_layers.py reports 16 violations, removed by M0 steps</t>
         </is>
       </c>
       <c r="G8" s="6" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="E30" s="6" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="F30" s="6" t="inlineStr">
         <is>
-          <t>M0; for comparing builds</t>
+          <t>F2; built, awaiting the owner's check on Windows</t>
         </is>
       </c>
       <c r="G30" s="6" t="inlineStr">
@@ -1931,12 +1931,12 @@
       </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F31" s="6" t="inlineStr">
         <is>
-          <t>Tools being installed</t>
+          <t>tools/check_mingw.sh; shader check runs clean</t>
         </is>
       </c>
       <c r="G31" s="6" t="inlineStr">
@@ -2057,12 +2057,12 @@
       </c>
       <c r="E34" s="6" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="F34" s="6" t="inlineStr">
         <is>
-          <t>M0</t>
+          <t>DESIGN.md carried over; CLAUDE.md drafted, awaiting the owner</t>
         </is>
       </c>
       <c r="G34" s="6" t="inlineStr">

--- a/docs/SCOPE_MOSCOW.xlsx
+++ b/docs/SCOPE_MOSCOW.xlsx
@@ -2057,12 +2057,12 @@
       </c>
       <c r="E34" s="6" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F34" s="6" t="inlineStr">
         <is>
-          <t>DESIGN.md carried over; CLAUDE.md drafted, awaiting the owner</t>
+          <t>CLAUDE.md and DESIGN.md done; DECISIONS.md done</t>
         </is>
       </c>
       <c r="G34" s="6" t="inlineStr">

--- a/docs/SCOPE_MOSCOW.xlsx
+++ b/docs/SCOPE_MOSCOW.xlsx
@@ -977,12 +977,12 @@
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F8" s="6" t="inlineStr">
         <is>
-          <t>tools/check_layers.py reports 16 violations, removed by M0 steps</t>
+          <t>0 violations; check_layers.py runs in tests/run.sh</t>
         </is>
       </c>
       <c r="G8" s="6" t="inlineStr">
@@ -1061,12 +1061,12 @@
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F10" s="6" t="inlineStr">
         <is>
-          <t>Approved with the foundations</t>
+          <t>M0.9: worldfile v1 with a game section; Voxistics loaders removed</t>
         </is>
       </c>
       <c r="G10" s="6" t="inlineStr">

--- a/docs/SCOPE_MOSCOW.xlsx
+++ b/docs/SCOPE_MOSCOW.xlsx
@@ -2470,7 +2470,7 @@
       </c>
       <c r="F44" s="6" t="inlineStr">
         <is>
-          <t>Served Voxistics features</t>
+          <t>Served Voxistics features; accessibility no longer a standing rule (D24)</t>
         </is>
       </c>
       <c r="G44" s="6" t="inlineStr">
@@ -2565,64 +2565,256 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="6" t="n"/>
-      <c r="B47" s="6" t="n"/>
-      <c r="C47" s="6" t="n"/>
-      <c r="D47" s="6" t="n"/>
-      <c r="E47" s="6" t="n"/>
-      <c r="F47" s="6" t="n"/>
-      <c r="G47" s="6" t="n"/>
-      <c r="H47" s="6" t="n"/>
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>W046</t>
+        </is>
+      </c>
+      <c r="B47" s="6" t="inlineStr">
+        <is>
+          <t>Engine</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="inlineStr">
+        <is>
+          <t>Graphics minimum: Direct3D feature level 11.0, shader model 5.0</t>
+        </is>
+      </c>
+      <c r="D47" s="6" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="E47" s="6" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="F47" s="6" t="inlineStr">
+        <is>
+          <t>M0.16 (D20)</t>
+        </is>
+      </c>
+      <c r="G47" s="6" t="inlineStr">
+        <is>
+          <t>Decisions D20</t>
+        </is>
+      </c>
+      <c r="H47" s="6" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
     </row>
     <row r="48">
-      <c r="A48" s="6" t="n"/>
-      <c r="B48" s="6" t="n"/>
-      <c r="C48" s="6" t="n"/>
-      <c r="D48" s="6" t="n"/>
-      <c r="E48" s="6" t="n"/>
-      <c r="F48" s="6" t="n"/>
-      <c r="G48" s="6" t="n"/>
-      <c r="H48" s="6" t="n"/>
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>W047</t>
+        </is>
+      </c>
+      <c r="B48" s="6" t="inlineStr">
+        <is>
+          <t>Engine</t>
+        </is>
+      </c>
+      <c r="C48" s="6" t="inlineStr">
+        <is>
+          <t>Harmless reads of OS limits only (thread count, video-memory budget); never kept or shown</t>
+        </is>
+      </c>
+      <c r="D48" s="6" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="E48" s="6" t="inlineStr">
+        <is>
+          <t>In progress</t>
+        </is>
+      </c>
+      <c r="F48" s="6" t="inlineStr">
+        <is>
+          <t>Standing rule (D21)</t>
+        </is>
+      </c>
+      <c r="G48" s="6" t="inlineStr">
+        <is>
+          <t>Decisions D21</t>
+        </is>
+      </c>
+      <c r="H48" s="6" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
     </row>
     <row r="49">
-      <c r="A49" s="6" t="n"/>
-      <c r="B49" s="6" t="n"/>
-      <c r="C49" s="6" t="n"/>
-      <c r="D49" s="6" t="n"/>
-      <c r="E49" s="6" t="n"/>
-      <c r="F49" s="6" t="n"/>
-      <c r="G49" s="6" t="n"/>
-      <c r="H49" s="6" t="n"/>
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>W048</t>
+        </is>
+      </c>
+      <c r="B49" s="6" t="inlineStr">
+        <is>
+          <t>Engine</t>
+        </is>
+      </c>
+      <c r="C49" s="6" t="inlineStr">
+        <is>
+          <t>No online play, no network code</t>
+        </is>
+      </c>
+      <c r="D49" s="6" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="E49" s="6" t="inlineStr">
+        <is>
+          <t>In progress</t>
+        </is>
+      </c>
+      <c r="F49" s="6" t="inlineStr">
+        <is>
+          <t>Standing rule, never 'done' (D23)</t>
+        </is>
+      </c>
+      <c r="G49" s="6" t="inlineStr">
+        <is>
+          <t>Decisions D23</t>
+        </is>
+      </c>
+      <c r="H49" s="6" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
     </row>
     <row r="50">
-      <c r="A50" s="6" t="n"/>
-      <c r="B50" s="6" t="n"/>
-      <c r="C50" s="6" t="n"/>
-      <c r="D50" s="6" t="n"/>
-      <c r="E50" s="6" t="n"/>
-      <c r="F50" s="6" t="n"/>
-      <c r="G50" s="6" t="n"/>
-      <c r="H50" s="6" t="n"/>
+      <c r="A50" s="6" t="inlineStr">
+        <is>
+          <t>W049</t>
+        </is>
+      </c>
+      <c r="B50" s="6" t="inlineStr">
+        <is>
+          <t>Sound</t>
+        </is>
+      </c>
+      <c r="C50" s="6" t="inlineStr">
+        <is>
+          <t>Synthesized sound only: no recorded or sampled audio</t>
+        </is>
+      </c>
+      <c r="D50" s="6" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="E50" s="6" t="inlineStr">
+        <is>
+          <t>In progress</t>
+        </is>
+      </c>
+      <c r="F50" s="6" t="inlineStr">
+        <is>
+          <t>Standing rule, never 'done' (D25)</t>
+        </is>
+      </c>
+      <c r="G50" s="6" t="inlineStr">
+        <is>
+          <t>Decisions D25</t>
+        </is>
+      </c>
+      <c r="H50" s="6" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
     </row>
     <row r="51">
-      <c r="A51" s="6" t="n"/>
-      <c r="B51" s="6" t="n"/>
-      <c r="C51" s="6" t="n"/>
-      <c r="D51" s="6" t="n"/>
-      <c r="E51" s="6" t="n"/>
-      <c r="F51" s="6" t="n"/>
-      <c r="G51" s="6" t="n"/>
-      <c r="H51" s="6" t="n"/>
+      <c r="A51" s="6" t="inlineStr">
+        <is>
+          <t>W050</t>
+        </is>
+      </c>
+      <c r="B51" s="6" t="inlineStr">
+        <is>
+          <t>Menus</t>
+        </is>
+      </c>
+      <c r="C51" s="6" t="inlineStr">
+        <is>
+          <t>Text ready for any language: string table, wider font atlas</t>
+        </is>
+      </c>
+      <c r="D51" s="6" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="E51" s="6" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="F51" s="6" t="inlineStr">
+        <is>
+          <t>M1 step 0 (D26)</t>
+        </is>
+      </c>
+      <c r="G51" s="6" t="inlineStr">
+        <is>
+          <t>Decisions D26</t>
+        </is>
+      </c>
+      <c r="H51" s="6" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
     </row>
     <row r="52">
-      <c r="A52" s="6" t="n"/>
-      <c r="B52" s="6" t="n"/>
-      <c r="C52" s="6" t="n"/>
-      <c r="D52" s="6" t="n"/>
-      <c r="E52" s="6" t="n"/>
-      <c r="F52" s="6" t="n"/>
-      <c r="G52" s="6" t="n"/>
-      <c r="H52" s="6" t="n"/>
+      <c r="A52" s="6" t="inlineStr">
+        <is>
+          <t>W051</t>
+        </is>
+      </c>
+      <c r="B52" s="6" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="C52" s="6" t="inlineStr">
+        <is>
+          <t>SOP binding, two tiers; hooks capped and listed</t>
+        </is>
+      </c>
+      <c r="D52" s="6" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="E52" s="6" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F52" s="6" t="inlineStr">
+        <is>
+          <t>docs/SOP.md; FOUNDATIONS.md 2.1 (D27)</t>
+        </is>
+      </c>
+      <c r="G52" s="6" t="inlineStr">
+        <is>
+          <t>Decisions D27</t>
+        </is>
+      </c>
+      <c r="H52" s="6" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="6" t="n"/>

--- a/docs/SCOPE_MOSCOW.xlsx
+++ b/docs/SCOPE_MOSCOW.xlsx
@@ -814,7 +814,7 @@
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Frames before and after must match, minus removed features</t>
+          <t>M0 steps done; awaiting the owner's Windows build and checklist</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="F6" s="6" t="inlineStr">
         <is>
-          <t>Checklist T12, T13</t>
+          <t>Interpolated rendering in M0.12; frame cap only with vsync off</t>
         </is>
       </c>
       <c r="G6" s="6" t="inlineStr">
@@ -935,12 +935,12 @@
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>M0</t>
+          <t>M0.10</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
@@ -1103,12 +1103,12 @@
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
-          <t>Approved with the foundations</t>
+          <t>M0.13, with a native test</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
@@ -1767,12 +1767,12 @@
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F27" s="6" t="inlineStr">
         <is>
-          <t>M0</t>
+          <t>M0.14; awaiting the feel check (C5)</t>
         </is>
       </c>
       <c r="G27" s="6" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F35" s="6" t="inlineStr">
         <is>
-          <t>M0</t>
+          <t>M0.11</t>
         </is>
       </c>
       <c r="G35" s="6" t="inlineStr">
@@ -2587,12 +2587,12 @@
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F47" s="6" t="inlineStr">
         <is>
-          <t>M0.16 (D20)</t>
+          <t>M0.16; awaiting the Windows build to confirm D3DCompile accepts SM5</t>
         </is>
       </c>
       <c r="G47" s="6" t="inlineStr">

--- a/docs/SCOPE_MOSCOW.xlsx
+++ b/docs/SCOPE_MOSCOW.xlsx
@@ -809,12 +809,12 @@
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>M0 steps done; awaiting the owner's Windows build and checklist</t>
+          <t>M0 done, run on the owner's machine 2026-09-25</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
@@ -1608,7 +1608,7 @@
       </c>
       <c r="F23" s="6" t="inlineStr">
         <is>
-          <t>Checklist T7</t>
+          <t>Checklist T7. Louder and brighter (D29); still subtle, owner decides the ceiling in M1 step 1.1</t>
         </is>
       </c>
       <c r="G23" s="6" t="inlineStr">
@@ -1799,7 +1799,7 @@
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>Hotbar and material library carried over</t>
+          <t>Choose materials from the library menu; hotbar kept for now</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
@@ -1812,15 +1812,19 @@
           <t>Not started</t>
         </is>
       </c>
-      <c r="F28" s="6" t="n"/>
+      <c r="F28" s="6" t="inlineStr">
+        <is>
+          <t>Owner (D30): materials are chosen in the library. The hotbar stays as a placeholder, possibly for other GUI later</t>
+        </is>
+      </c>
       <c r="G28" s="6" t="inlineStr">
         <is>
-          <t>Outline 7</t>
+          <t>Decisions D30</t>
         </is>
       </c>
       <c r="H28" s="6" t="inlineStr">
         <is>
-          <t>Claude (proposed)</t>
+          <t>Owner</t>
         </is>
       </c>
     </row>

--- a/docs/SCOPE_MOSCOW.xlsx
+++ b/docs/SCOPE_MOSCOW.xlsx
@@ -1608,7 +1608,7 @@
       </c>
       <c r="F23" s="6" t="inlineStr">
         <is>
-          <t>Checklist T7. Louder and brighter (D29); still subtle, owner decides the ceiling in M1 step 1.1</t>
+          <t>Checklist T7. Louder and brighter (D29); still subtle, owner decides the ceiling in M1 step 1.12 (D31)</t>
         </is>
       </c>
       <c r="G23" s="6" t="inlineStr">

--- a/docs/SCOPE_MOSCOW.xlsx
+++ b/docs/SCOPE_MOSCOW.xlsx
@@ -1687,12 +1687,12 @@
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="F25" s="6" t="inlineStr">
         <is>
-          <t>So busy moments never click or cut out</t>
+          <t>Built in M1.1 (own thread, mailbox, 48-voice cap tested); awaiting the owner's Ctrl+F3 report</t>
         </is>
       </c>
       <c r="G25" s="6" t="inlineStr">

--- a/docs/SCOPE_MOSCOW.xlsx
+++ b/docs/SCOPE_MOSCOW.xlsx
@@ -1187,12 +1187,12 @@
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>One-block cells; detail is visual only</t>
+          <t>Mesher built and tested (M1.2, facetmesh.h); in game from M1.5</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
@@ -1229,12 +1229,12 @@
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
-          <t>Subdivide only where it shows; set from preview-tool counts</t>
+          <t>Detail cut on lumpy materials only; stitched; 308k tris within 96 blocks in the preview</t>
         </is>
       </c>
       <c r="G14" s="6" t="inlineStr">
@@ -1977,12 +1977,12 @@
       </c>
       <c r="E32" s="6" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F32" s="6" t="inlineStr">
         <is>
-          <t>M1's first deliverable</t>
+          <t>M1.2: tools/facet_preview.sh; pictures in docs/pictures/m1_2</t>
         </is>
       </c>
       <c r="G32" s="6" t="inlineStr">

--- a/docs/SCOPE_MOSCOW.xlsx
+++ b/docs/SCOPE_MOSCOW.xlsx
@@ -2821,14 +2821,46 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="6" t="n"/>
-      <c r="B53" s="6" t="n"/>
-      <c r="C53" s="6" t="n"/>
-      <c r="D53" s="6" t="n"/>
-      <c r="E53" s="6" t="n"/>
-      <c r="F53" s="6" t="n"/>
-      <c r="G53" s="6" t="n"/>
-      <c r="H53" s="6" t="n"/>
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>W052</t>
+        </is>
+      </c>
+      <c r="B53" s="6" t="inlineStr">
+        <is>
+          <t>Looks</t>
+        </is>
+      </c>
+      <c r="C53" s="6" t="inlineStr">
+        <is>
+          <t>Twelve starting materials, chosen on contact sheets</t>
+        </is>
+      </c>
+      <c r="D53" s="6" t="inlineStr">
+        <is>
+          <t>Should</t>
+        </is>
+      </c>
+      <c r="E53" s="6" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F53" s="6" t="inlineStr">
+        <is>
+          <t>D36, provisional until the owner confirms; docs/pictures/m1_3</t>
+        </is>
+      </c>
+      <c r="G53" s="6" t="inlineStr">
+        <is>
+          <t>Decisions D36</t>
+        </is>
+      </c>
+      <c r="H53" s="6" t="inlineStr">
+        <is>
+          <t>Claude (proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="6" t="n"/>

--- a/docs/SCOPE_MOSCOW.xlsx
+++ b/docs/SCOPE_MOSCOW.xlsx
@@ -1019,12 +1019,12 @@
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
-          <t>Approved with the foundations</t>
+          <t>jobs.h (M1.4): terrain on job threads with epochs; meshes from M1.5</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
@@ -1355,12 +1355,12 @@
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>Replaces the flat plain; versioned generator</t>
+          <t>walkgrid-hills v1 (M1.4, D37): seeded, pinned; pictures docs/pictures/m1_4</t>
         </is>
       </c>
       <c r="G17" s="6" t="inlineStr">

--- a/docs/SCOPE_MOSCOW.xlsx
+++ b/docs/SCOPE_MOSCOW.xlsx
@@ -1192,7 +1192,7 @@
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>Mesher built and tested (M1.2, facetmesh.h); in game from M1.5</t>
+          <t>In game from M1.5 (groundmesh.h, world shader); collision and picking in M1.7</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
@@ -1439,10 +1439,14 @@
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="F19" s="6" t="n"/>
+          <t>In progress</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>M1.5: smooth (trilinear, 4x anisotropic) at every distance (D38); up close the 32 px art reads blurry: owner to judge</t>
+        </is>
+      </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
           <t>Outline D8</t>

--- a/docs/SCOPE_MOSCOW.xlsx
+++ b/docs/SCOPE_MOSCOW.xlsx
@@ -1481,12 +1481,12 @@
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="F20" s="6" t="inlineStr">
         <is>
-          <t>Checklist T3</t>
+          <t>Built in M1.6 (height layers, 3-material blend in the shader); owner to judge in game (T3)</t>
         </is>
       </c>
       <c r="G20" s="6" t="inlineStr">
@@ -1523,12 +1523,12 @@
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="F21" s="6" t="inlineStr">
         <is>
-          <t>Checklist T5</t>
+          <t>Built in M1.6 (column tops, horizon sky light per vertex); owner to judge (T5)</t>
         </is>
       </c>
       <c r="G21" s="6" t="inlineStr">

--- a/docs/SCOPE_MOSCOW.xlsx
+++ b/docs/SCOPE_MOSCOW.xlsx
@@ -1271,12 +1271,12 @@
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>Checklist T6</t>
+          <t>On facets from M1.7 (collide.h, D39); scripted walks clean; owner to judge the feel (T6)</t>
         </is>
       </c>
       <c r="G15" s="6" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="F16" s="6" t="inlineStr">
         <is>
-          <t>Checklist T8</t>
+          <t>Picking on facets from M1.7; owner to check it lands where aimed (T8)</t>
         </is>
       </c>
       <c r="G16" s="6" t="inlineStr">

--- a/docs/SCOPE_MOSCOW.xlsx
+++ b/docs/SCOPE_MOSCOW.xlsx
@@ -1234,7 +1234,7 @@
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
-          <t>Detail cut on lumpy materials only; stitched; 308k tris within 96 blocks in the preview</t>
+          <t>Detail bands built (M1.8, D40): levels by distance with hysteresis, crack-free seams at any level pairing, FINE DETAIL setting</t>
         </is>
       </c>
       <c r="G14" s="6" t="inlineStr">

--- a/docs/SCOPE_MOSCOW.xlsx
+++ b/docs/SCOPE_MOSCOW.xlsx
@@ -1813,12 +1813,12 @@
       </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="F28" s="6" t="inlineStr">
         <is>
-          <t>Owner (D30): materials are chosen in the library. The hotbar stays as a placeholder, possibly for other GUI later</t>
+          <t>Owner (D30): materials chosen in the library (twelve, M1.9, faceted-lump icons); the hotbar stays as a placeholder</t>
         </is>
       </c>
       <c r="G28" s="6" t="inlineStr">

--- a/docs/SCOPE_MOSCOW.xlsx
+++ b/docs/SCOPE_MOSCOW.xlsx
@@ -2763,12 +2763,12 @@
       </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F51" s="6" t="inlineStr">
         <is>
-          <t>M1 step 0 (D26)</t>
+          <t>M1 step 1.10 (D26, D42): assets/text, strtable.*, atlas from the table, check_strings.py. Awaiting the owner's check (test language)</t>
         </is>
       </c>
       <c r="G51" s="6" t="inlineStr">

--- a/docs/SCOPE_MOSCOW.xlsx
+++ b/docs/SCOPE_MOSCOW.xlsx
@@ -2553,12 +2553,12 @@
       </c>
       <c r="E46" s="6" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F46" s="6" t="inlineStr">
         <is>
-          <t>Frustum culling exists; hidden-chunk skipping and heading-aware loading in M1</t>
+          <t>Frustum culling; hidden-chunk skipping and heading-aware loading built in M1 step 1.11 (D43). Awaiting a Ctrl+F3 report (CHUNKS HIDDEN)</t>
         </is>
       </c>
       <c r="G46" s="6" t="inlineStr">

--- a/docs/SCOPE_MOSCOW.xlsx
+++ b/docs/SCOPE_MOSCOW.xlsx
@@ -1397,12 +1397,12 @@
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="F18" s="6" t="inlineStr">
         <is>
-          <t>Checklist T4</t>
+          <t>Carried over and building; awaiting the owner's checklist T4 (M1.12)</t>
         </is>
       </c>
       <c r="G18" s="6" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="F22" s="6" t="inlineStr">
         <is>
-          <t>Checklist T10</t>
+          <t>Carried over and building; awaiting the owner's checklist T10 (M1.12)</t>
         </is>
       </c>
       <c r="G22" s="6" t="inlineStr">
@@ -1607,12 +1607,12 @@
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
         <is>
-          <t>Checklist T7. Louder and brighter (D29); still subtle, owner decides the ceiling in M1 step 1.12 (D31)</t>
+          <t>Checklist T7. Louder and brighter (D29). Clips at three footstep ceilings made in M1.12 (D44); the game stays at -21 dB until the owner picks</t>
         </is>
       </c>
       <c r="G23" s="6" t="inlineStr">
@@ -1649,12 +1649,12 @@
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="F24" s="6" t="inlineStr">
         <is>
-          <t>Checklist T9</t>
+          <t>Carried over and building; awaiting the owner's checklist T9 (M1.12)</t>
         </is>
       </c>
       <c r="G24" s="6" t="inlineStr">
@@ -1855,12 +1855,12 @@
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="F29" s="6" t="inlineStr">
         <is>
-          <t>Carried over; checklist T11</t>
+          <t>Carried over and building; awaiting the owner's checklist T11 (M1.12)</t>
         </is>
       </c>
       <c r="G29" s="6" t="inlineStr">
@@ -2867,14 +2867,46 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="6" t="n"/>
-      <c r="B54" s="6" t="n"/>
-      <c r="C54" s="6" t="n"/>
-      <c r="D54" s="6" t="n"/>
-      <c r="E54" s="6" t="n"/>
-      <c r="F54" s="6" t="n"/>
-      <c r="G54" s="6" t="n"/>
-      <c r="H54" s="6" t="n"/>
+      <c r="A54" s="6" t="inlineStr">
+        <is>
+          <t>W053</t>
+        </is>
+      </c>
+      <c r="B54" s="6" t="inlineStr">
+        <is>
+          <t>Sound</t>
+        </is>
+      </c>
+      <c r="C54" s="6" t="inlineStr">
+        <is>
+          <t>Sand sounds like sand underfoot (its own soft hiss)</t>
+        </is>
+      </c>
+      <c r="D54" s="6" t="inlineStr">
+        <is>
+          <t>Could</t>
+        </is>
+      </c>
+      <c r="E54" s="6" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F54" s="6" t="inlineStr">
+        <is>
+          <t>Added in M1.12 so T7's four grounds differ (D44); owner to keep or drop</t>
+        </is>
+      </c>
+      <c r="G54" s="6" t="inlineStr">
+        <is>
+          <t>Sound palette R1</t>
+        </is>
+      </c>
+      <c r="H54" s="6" t="inlineStr">
+        <is>
+          <t>Claude (proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="6" t="n"/>

--- a/docs/SCOPE_MOSCOW.xlsx
+++ b/docs/SCOPE_MOSCOW.xlsx
@@ -2894,7 +2894,7 @@
       </c>
       <c r="F54" s="6" t="inlineStr">
         <is>
-          <t>Added in M1.12 so T7's four grounds differ (D44); owner to keep or drop</t>
+          <t>Added in M1.12 so T7's four grounds differ (D44); waits until the owner can hear footsteps (D48)</t>
         </is>
       </c>
       <c r="G54" s="6" t="inlineStr">
@@ -2909,14 +2909,46 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="6" t="n"/>
-      <c r="B55" s="6" t="n"/>
-      <c r="C55" s="6" t="n"/>
-      <c r="D55" s="6" t="n"/>
-      <c r="E55" s="6" t="n"/>
-      <c r="F55" s="6" t="n"/>
-      <c r="G55" s="6" t="n"/>
-      <c r="H55" s="6" t="n"/>
+      <c r="A55" s="6" t="inlineStr">
+        <is>
+          <t>W054</t>
+        </is>
+      </c>
+      <c r="B55" s="6" t="inlineStr">
+        <is>
+          <t>World</t>
+        </is>
+      </c>
+      <c r="C55" s="6" t="inlineStr">
+        <is>
+          <t>Weather: kinds of weather orchestrated by a weather state that sets the sky, cloud, fog, light and sound knobs; cheap tricks only, nothing volumetric</t>
+        </is>
+      </c>
+      <c r="D55" s="6" t="inlineStr">
+        <is>
+          <t>Could</t>
+        </is>
+      </c>
+      <c r="E55" s="6" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="F55" s="6" t="inlineStr">
+        <is>
+          <t>Later (owner, D58/D59). The cloud layers and jet stream are its first knobs. Design notes are a helper-agent task (PROJECT_NOTES 9)</t>
+        </is>
+      </c>
+      <c r="G55" s="6" t="inlineStr">
+        <is>
+          <t>DESIGN Part XIII</t>
+        </is>
+      </c>
+      <c r="H55" s="6" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="6" t="n"/>

--- a/docs/SCOPE_MOSCOW.xlsx
+++ b/docs/SCOPE_MOSCOW.xlsx
@@ -2951,14 +2951,46 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="6" t="n"/>
-      <c r="B56" s="6" t="n"/>
-      <c r="C56" s="6" t="n"/>
-      <c r="D56" s="6" t="n"/>
-      <c r="E56" s="6" t="n"/>
-      <c r="F56" s="6" t="n"/>
-      <c r="G56" s="6" t="n"/>
-      <c r="H56" s="6" t="n"/>
+      <c r="A56" s="6" t="inlineStr">
+        <is>
+          <t>W055</t>
+        </is>
+      </c>
+      <c r="B56" s="6" t="inlineStr">
+        <is>
+          <t>World</t>
+        </is>
+      </c>
+      <c r="C56" s="6" t="inlineStr">
+        <is>
+          <t>Gentle slopes roll instead of terracing, with player edits kept crisp</t>
+        </is>
+      </c>
+      <c r="D56" s="6" t="inlineStr">
+        <is>
+          <t>Won't</t>
+        </is>
+      </c>
+      <c r="E56" s="6" t="inlineStr">
+        <is>
+          <t>Parked</t>
+        </is>
+      </c>
+      <c r="F56" s="6" t="inlineStr">
+        <is>
+          <t>D62: back burner until a nicer way. FacetShape::terrace is built but off (it softens one-cell edits)</t>
+        </is>
+      </c>
+      <c r="G56" s="6" t="inlineStr">
+        <is>
+          <t>DESIGN 23.1</t>
+        </is>
+      </c>
+      <c r="H56" s="6" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="6" t="n"/>

--- a/docs/SCOPE_MOSCOW.xlsx
+++ b/docs/SCOPE_MOSCOW.xlsx
@@ -2023,12 +2023,12 @@
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F33" s="6" t="inlineStr">
         <is>
-          <t>Awaits the owner at each milestone</t>
+          <t>Two Ctrl+F3 reports from the owner, 2026-09-26 (199 fps, no hitches): docs/COST_LEDGER.md</t>
         </is>
       </c>
       <c r="G33" s="6" t="inlineStr">

--- a/docs/SCOPE_MOSCOW.xlsx
+++ b/docs/SCOPE_MOSCOW.xlsx
@@ -2993,14 +2993,46 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="6" t="n"/>
-      <c r="B57" s="6" t="n"/>
-      <c r="C57" s="6" t="n"/>
-      <c r="D57" s="6" t="n"/>
-      <c r="E57" s="6" t="n"/>
-      <c r="F57" s="6" t="n"/>
-      <c r="G57" s="6" t="n"/>
-      <c r="H57" s="6" t="n"/>
+      <c r="A57" s="6" t="inlineStr">
+        <is>
+          <t>W056</t>
+        </is>
+      </c>
+      <c r="B57" s="6" t="inlineStr">
+        <is>
+          <t>Looks</t>
+        </is>
+      </c>
+      <c r="C57" s="6" t="inlineStr">
+        <is>
+          <t>Shadowed ground keeps its shape: fill light (brighter sky toward the sun, warm bounce from sunlit ground), shadow less blue</t>
+        </is>
+      </c>
+      <c r="D57" s="6" t="inlineStr">
+        <is>
+          <t>Could</t>
+        </is>
+      </c>
+      <c r="E57" s="6" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F57" s="6" t="inlineStr">
+        <is>
+          <t>D63; replaces what screen-space AO was faking, without the golf-ball dimples. Awaiting the owner's look in game</t>
+        </is>
+      </c>
+      <c r="G57" s="6" t="inlineStr">
+        <is>
+          <t>DESIGN 4.9</t>
+        </is>
+      </c>
+      <c r="H57" s="6" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="6" t="n"/>

--- a/docs/SCOPE_MOSCOW.xlsx
+++ b/docs/SCOPE_MOSCOW.xlsx
@@ -3035,14 +3035,46 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="6" t="n"/>
-      <c r="B58" s="6" t="n"/>
-      <c r="C58" s="6" t="n"/>
-      <c r="D58" s="6" t="n"/>
-      <c r="E58" s="6" t="n"/>
-      <c r="F58" s="6" t="n"/>
-      <c r="G58" s="6" t="n"/>
-      <c r="H58" s="6" t="n"/>
+      <c r="A58" s="6" t="inlineStr">
+        <is>
+          <t>W057</t>
+        </is>
+      </c>
+      <c r="B58" s="6" t="inlineStr">
+        <is>
+          <t>Platform</t>
+        </is>
+      </c>
+      <c r="C58" s="6" t="inlineStr">
+        <is>
+          <t>F2 screenshots without a stall: the PNG is encoded on a job thread</t>
+        </is>
+      </c>
+      <c r="D58" s="6" t="inlineStr">
+        <is>
+          <t>Could</t>
+        </is>
+      </c>
+      <c r="E58" s="6" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F58" s="6" t="inlineStr">
+        <is>
+          <t>The owner's report showed 70-100 ms hitches from F2; now only the read-back runs on the frame. Toast when on disk</t>
+        </is>
+      </c>
+      <c r="G58" s="6" t="inlineStr">
+        <is>
+          <t>DESIGN 7.2.1</t>
+        </is>
+      </c>
+      <c r="H58" s="6" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="6" t="n"/>

--- a/docs/SCOPE_MOSCOW.xlsx
+++ b/docs/SCOPE_MOSCOW.xlsx
@@ -3077,14 +3077,46 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="6" t="n"/>
-      <c r="B59" s="6" t="n"/>
-      <c r="C59" s="6" t="n"/>
-      <c r="D59" s="6" t="n"/>
-      <c r="E59" s="6" t="n"/>
-      <c r="F59" s="6" t="n"/>
-      <c r="G59" s="6" t="n"/>
-      <c r="H59" s="6" t="n"/>
+      <c r="A59" s="6" t="inlineStr">
+        <is>
+          <t>W058</t>
+        </is>
+      </c>
+      <c r="B59" s="6" t="inlineStr">
+        <is>
+          <t>Looks</t>
+        </is>
+      </c>
+      <c r="C59" s="6" t="inlineStr">
+        <is>
+          <t>Distant ground keeps its colour: narrower edge fade, no sun glow in the ground's fog</t>
+        </is>
+      </c>
+      <c r="D59" s="6" t="inlineStr">
+        <is>
+          <t>Could</t>
+        </is>
+      </c>
+      <c r="E59" s="6" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F59" s="6" t="inlineStr">
+        <is>
+          <t>D64. The real fix for seeing far is cheap distant ground (a far, coarse ring): a future plan</t>
+        </is>
+      </c>
+      <c r="G59" s="6" t="inlineStr">
+        <is>
+          <t>DESIGN 4.9</t>
+        </is>
+      </c>
+      <c r="H59" s="6" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="6" t="n"/>

--- a/docs/SCOPE_MOSCOW.xlsx
+++ b/docs/SCOPE_MOSCOW.xlsx
@@ -3119,94 +3119,382 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="6" t="n"/>
-      <c r="B60" s="6" t="n"/>
-      <c r="C60" s="6" t="n"/>
-      <c r="D60" s="6" t="n"/>
-      <c r="E60" s="6" t="n"/>
-      <c r="F60" s="6" t="n"/>
-      <c r="G60" s="6" t="n"/>
-      <c r="H60" s="6" t="n"/>
+      <c r="A60" s="6" t="inlineStr">
+        <is>
+          <t>W059</t>
+        </is>
+      </c>
+      <c r="B60" s="6" t="inlineStr">
+        <is>
+          <t>Sky</t>
+        </is>
+      </c>
+      <c r="C60" s="6" t="inlineStr">
+        <is>
+          <t>Clouds that live: faster drift, shapes that form, stretch and break up downwind</t>
+        </is>
+      </c>
+      <c r="D60" s="6" t="inlineStr">
+        <is>
+          <t>Could</t>
+        </is>
+      </c>
+      <c r="E60" s="6" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="F60" s="6" t="inlineStr">
+        <is>
+          <t>PLAN_LOOK A; waits for the owner's go</t>
+        </is>
+      </c>
+      <c r="G60" s="6" t="inlineStr">
+        <is>
+          <t>DESIGN 4.9</t>
+        </is>
+      </c>
+      <c r="H60" s="6" t="inlineStr">
+        <is>
+          <t>Claude (proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="61">
-      <c r="A61" s="6" t="n"/>
-      <c r="B61" s="6" t="n"/>
-      <c r="C61" s="6" t="n"/>
-      <c r="D61" s="6" t="n"/>
-      <c r="E61" s="6" t="n"/>
-      <c r="F61" s="6" t="n"/>
-      <c r="G61" s="6" t="n"/>
-      <c r="H61" s="6" t="n"/>
+      <c r="A61" s="6" t="inlineStr">
+        <is>
+          <t>W060</t>
+        </is>
+      </c>
+      <c r="B61" s="6" t="inlineStr">
+        <is>
+          <t>Sky</t>
+        </is>
+      </c>
+      <c r="C61" s="6" t="inlineStr">
+        <is>
+          <t>High streaks shorter and patchy, no ray-like convergence toward the sun</t>
+        </is>
+      </c>
+      <c r="D61" s="6" t="inlineStr">
+        <is>
+          <t>Could</t>
+        </is>
+      </c>
+      <c r="E61" s="6" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="F61" s="6" t="inlineStr">
+        <is>
+          <t>PLAN_LOOK B</t>
+        </is>
+      </c>
+      <c r="G61" s="6" t="inlineStr">
+        <is>
+          <t>DESIGN 4.9</t>
+        </is>
+      </c>
+      <c r="H61" s="6" t="inlineStr">
+        <is>
+          <t>Claude (proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="62">
-      <c r="A62" s="6" t="n"/>
-      <c r="B62" s="6" t="n"/>
-      <c r="C62" s="6" t="n"/>
-      <c r="D62" s="6" t="n"/>
-      <c r="E62" s="6" t="n"/>
-      <c r="F62" s="6" t="n"/>
-      <c r="G62" s="6" t="n"/>
-      <c r="H62" s="6" t="n"/>
+      <c r="A62" s="6" t="inlineStr">
+        <is>
+          <t>W061</t>
+        </is>
+      </c>
+      <c r="B62" s="6" t="inlineStr">
+        <is>
+          <t>Sky</t>
+        </is>
+      </c>
+      <c r="C62" s="6" t="inlineStr">
+        <is>
+          <t>Low clouds soft-edged and rim-lit, never flat puddles</t>
+        </is>
+      </c>
+      <c r="D62" s="6" t="inlineStr">
+        <is>
+          <t>Could</t>
+        </is>
+      </c>
+      <c r="E62" s="6" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="F62" s="6" t="inlineStr">
+        <is>
+          <t>PLAN_LOOK C</t>
+        </is>
+      </c>
+      <c r="G62" s="6" t="inlineStr">
+        <is>
+          <t>DESIGN 4.9</t>
+        </is>
+      </c>
+      <c r="H62" s="6" t="inlineStr">
+        <is>
+          <t>Claude (proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="63">
-      <c r="A63" s="6" t="n"/>
-      <c r="B63" s="6" t="n"/>
-      <c r="C63" s="6" t="n"/>
-      <c r="D63" s="6" t="n"/>
-      <c r="E63" s="6" t="n"/>
-      <c r="F63" s="6" t="n"/>
-      <c r="G63" s="6" t="n"/>
-      <c r="H63" s="6" t="n"/>
+      <c r="A63" s="6" t="inlineStr">
+        <is>
+          <t>W062</t>
+        </is>
+      </c>
+      <c r="B63" s="6" t="inlineStr">
+        <is>
+          <t>Looks</t>
+        </is>
+      </c>
+      <c r="C63" s="6" t="inlineStr">
+        <is>
+          <t>Clean material edges: a smooth noise-driven blend band, no thin streaks of one material in another</t>
+        </is>
+      </c>
+      <c r="D63" s="6" t="inlineStr">
+        <is>
+          <t>Could</t>
+        </is>
+      </c>
+      <c r="E63" s="6" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="F63" s="6" t="inlineStr">
+        <is>
+          <t>PLAN_LOOK D; the orange lines at the slate ridge</t>
+        </is>
+      </c>
+      <c r="G63" s="6" t="inlineStr">
+        <is>
+          <t>DESIGN 23.4</t>
+        </is>
+      </c>
+      <c r="H63" s="6" t="inlineStr">
+        <is>
+          <t>Claude (proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="64">
-      <c r="A64" s="6" t="n"/>
-      <c r="B64" s="6" t="n"/>
-      <c r="C64" s="6" t="n"/>
-      <c r="D64" s="6" t="n"/>
-      <c r="E64" s="6" t="n"/>
-      <c r="F64" s="6" t="n"/>
-      <c r="G64" s="6" t="n"/>
-      <c r="H64" s="6" t="n"/>
+      <c r="A64" s="6" t="inlineStr">
+        <is>
+          <t>W063</t>
+        </is>
+      </c>
+      <c r="B64" s="6" t="inlineStr">
+        <is>
+          <t>Looks</t>
+        </is>
+      </c>
+      <c r="C64" s="6" t="inlineStr">
+        <is>
+          <t>Textures without visible repetition: per-cell random shift and turn, and large-scale patches per material</t>
+        </is>
+      </c>
+      <c r="D64" s="6" t="inlineStr">
+        <is>
+          <t>Could</t>
+        </is>
+      </c>
+      <c r="E64" s="6" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="F64" s="6" t="inlineStr">
+        <is>
+          <t>PLAN_LOOK E</t>
+        </is>
+      </c>
+      <c r="G64" s="6" t="inlineStr">
+        <is>
+          <t>DESIGN 4.16</t>
+        </is>
+      </c>
+      <c r="H64" s="6" t="inlineStr">
+        <is>
+          <t>Claude (proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="65">
-      <c r="A65" s="6" t="n"/>
-      <c r="B65" s="6" t="n"/>
-      <c r="C65" s="6" t="n"/>
-      <c r="D65" s="6" t="n"/>
-      <c r="E65" s="6" t="n"/>
-      <c r="F65" s="6" t="n"/>
-      <c r="G65" s="6" t="n"/>
-      <c r="H65" s="6" t="n"/>
+      <c r="A65" s="6" t="inlineStr">
+        <is>
+          <t>W064</t>
+        </is>
+      </c>
+      <c r="B65" s="6" t="inlineStr">
+        <is>
+          <t>Looks</t>
+        </is>
+      </c>
+      <c r="C65" s="6" t="inlineStr">
+        <is>
+          <t>64-pixel material textures</t>
+        </is>
+      </c>
+      <c r="D65" s="6" t="inlineStr">
+        <is>
+          <t>Could</t>
+        </is>
+      </c>
+      <c r="E65" s="6" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="F65" s="6" t="inlineStr">
+        <is>
+          <t>PLAN_LOOK F; density to be decided by the owner</t>
+        </is>
+      </c>
+      <c r="G65" s="6" t="inlineStr">
+        <is>
+          <t>TEXTURE_BRIEF</t>
+        </is>
+      </c>
+      <c r="H65" s="6" t="inlineStr">
+        <is>
+          <t>Claude (proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="66">
-      <c r="A66" s="6" t="n"/>
-      <c r="B66" s="6" t="n"/>
-      <c r="C66" s="6" t="n"/>
-      <c r="D66" s="6" t="n"/>
-      <c r="E66" s="6" t="n"/>
-      <c r="F66" s="6" t="n"/>
-      <c r="G66" s="6" t="n"/>
-      <c r="H66" s="6" t="n"/>
+      <c r="A66" s="6" t="inlineStr">
+        <is>
+          <t>W065</t>
+        </is>
+      </c>
+      <c r="B66" s="6" t="inlineStr">
+        <is>
+          <t>Tools</t>
+        </is>
+      </c>
+      <c r="C66" s="6" t="inlineStr">
+        <is>
+          <t>Debug views: baked darkening only, shadows only, materials only</t>
+        </is>
+      </c>
+      <c r="D66" s="6" t="inlineStr">
+        <is>
+          <t>Could</t>
+        </is>
+      </c>
+      <c r="E66" s="6" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="F66" s="6" t="inlineStr">
+        <is>
+          <t>PLAN_LOOK G; to find the patches seen at noon</t>
+        </is>
+      </c>
+      <c r="G66" s="6" t="inlineStr">
+        <is>
+          <t>DESIGN Part XVI</t>
+        </is>
+      </c>
+      <c r="H66" s="6" t="inlineStr">
+        <is>
+          <t>Claude (proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="67">
-      <c r="A67" s="6" t="n"/>
-      <c r="B67" s="6" t="n"/>
-      <c r="C67" s="6" t="n"/>
-      <c r="D67" s="6" t="n"/>
-      <c r="E67" s="6" t="n"/>
-      <c r="F67" s="6" t="n"/>
-      <c r="G67" s="6" t="n"/>
-      <c r="H67" s="6" t="n"/>
+      <c r="A67" s="6" t="inlineStr">
+        <is>
+          <t>W066</t>
+        </is>
+      </c>
+      <c r="B67" s="6" t="inlineStr">
+        <is>
+          <t>Looks</t>
+        </is>
+      </c>
+      <c r="C67" s="6" t="inlineStr">
+        <is>
+          <t>Slate lighter and less saturated</t>
+        </is>
+      </c>
+      <c r="D67" s="6" t="inlineStr">
+        <is>
+          <t>Could</t>
+        </is>
+      </c>
+      <c r="E67" s="6" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="F67" s="6" t="inlineStr">
+        <is>
+          <t>PLAN_LOOK H</t>
+        </is>
+      </c>
+      <c r="G67" s="6" t="inlineStr">
+        <is>
+          <t>TEXTURE_BRIEF</t>
+        </is>
+      </c>
+      <c r="H67" s="6" t="inlineStr">
+        <is>
+          <t>Claude (proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="68">
-      <c r="A68" s="6" t="n"/>
-      <c r="B68" s="6" t="n"/>
-      <c r="C68" s="6" t="n"/>
-      <c r="D68" s="6" t="n"/>
-      <c r="E68" s="6" t="n"/>
-      <c r="F68" s="6" t="n"/>
-      <c r="G68" s="6" t="n"/>
-      <c r="H68" s="6" t="n"/>
+      <c r="A68" s="6" t="inlineStr">
+        <is>
+          <t>W067</t>
+        </is>
+      </c>
+      <c r="B68" s="6" t="inlineStr">
+        <is>
+          <t>World</t>
+        </is>
+      </c>
+      <c r="C68" s="6" t="inlineStr">
+        <is>
+          <t>A building layer: crisp placed blocks that sit on the faceted ground in a satisfying way</t>
+        </is>
+      </c>
+      <c r="D68" s="6" t="inlineStr">
+        <is>
+          <t>Won't</t>
+        </is>
+      </c>
+      <c r="E68" s="6" t="inlineStr">
+        <is>
+          <t>Parked</t>
+        </is>
+      </c>
+      <c r="F68" s="6" t="inlineStr">
+        <is>
+          <t>Owner's idea, 2026-09-26; questions in PLAN_LOOK. The Voxistics cube mesher and pieces were removed in M1.9 (D41)</t>
+        </is>
+      </c>
+      <c r="G68" s="6" t="inlineStr">
+        <is>
+          <t>DESIGN 4.15</t>
+        </is>
+      </c>
+      <c r="H68" s="6" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="6" t="n"/>

--- a/docs/SCOPE_MOSCOW.xlsx
+++ b/docs/SCOPE_MOSCOW.xlsx
@@ -3146,7 +3146,7 @@
       </c>
       <c r="F60" s="6" t="inlineStr">
         <is>
-          <t>PLAN_LOOK A; waits for the owner's go</t>
+          <t>PLAN_LOOK A; researched in docs/research/CLOUDS.md; real or compressed time is the owner's call</t>
         </is>
       </c>
       <c r="G60" s="6" t="inlineStr">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="F65" s="6" t="inlineStr">
         <is>
-          <t>PLAN_LOOK F; density to be decided by the owner</t>
+          <t>PLAN_LOOK F; 64 pixels per block (D65)</t>
         </is>
       </c>
       <c r="G65" s="6" t="inlineStr">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="H65" s="6" t="inlineStr">
         <is>
-          <t>Claude (proposed)</t>
+          <t>Owner</t>
         </is>
       </c>
     </row>

--- a/docs/SCOPE_MOSCOW.xlsx
+++ b/docs/SCOPE_MOSCOW.xlsx
@@ -3497,24 +3497,88 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="6" t="n"/>
-      <c r="B69" s="6" t="n"/>
-      <c r="C69" s="6" t="n"/>
-      <c r="D69" s="6" t="n"/>
-      <c r="E69" s="6" t="n"/>
-      <c r="F69" s="6" t="n"/>
-      <c r="G69" s="6" t="n"/>
-      <c r="H69" s="6" t="n"/>
+      <c r="A69" s="6" t="inlineStr">
+        <is>
+          <t>W068</t>
+        </is>
+      </c>
+      <c r="B69" s="6" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="C69" s="6" t="inlineStr">
+        <is>
+          <t>East Asian text: double-width glyph cells in the UI atlas and layout, for Chinese, Japanese and Korean</t>
+        </is>
+      </c>
+      <c r="D69" s="6" t="inlineStr">
+        <is>
+          <t>Could</t>
+        </is>
+      </c>
+      <c r="E69" s="6" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="F69" s="6" t="inlineStr">
+        <is>
+          <t>Owner: be inclusive of Asian and African languages. Translations T18-T21 (and Amharic, T33, if its script is wide) wait on it. Fonts per language via the font line</t>
+        </is>
+      </c>
+      <c r="G69" s="6" t="inlineStr">
+        <is>
+          <t>DESIGN 4.6.2</t>
+        </is>
+      </c>
+      <c r="H69" s="6" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
     </row>
     <row r="70">
-      <c r="A70" s="6" t="n"/>
-      <c r="B70" s="6" t="n"/>
-      <c r="C70" s="6" t="n"/>
-      <c r="D70" s="6" t="n"/>
-      <c r="E70" s="6" t="n"/>
-      <c r="F70" s="6" t="n"/>
-      <c r="G70" s="6" t="n"/>
-      <c r="H70" s="6" t="n"/>
+      <c r="A70" s="6" t="inlineStr">
+        <is>
+          <t>W069</t>
+        </is>
+      </c>
+      <c r="B70" s="6" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="C70" s="6" t="inlineStr">
+        <is>
+          <t>Scripts that need shaping or stacked marks (Devanagari, Thai, Arabic right-to-left, combining tone marks as in some Yoruba)</t>
+        </is>
+      </c>
+      <c r="D70" s="6" t="inlineStr">
+        <is>
+          <t>Won't</t>
+        </is>
+      </c>
+      <c r="E70" s="6" t="inlineStr">
+        <is>
+          <t>Parked</t>
+        </is>
+      </c>
+      <c r="F70" s="6" t="inlineStr">
+        <is>
+          <t>A per-glyph atlas can't join or reorder letters; needs a shaping step. Kept so it isn't forgotten</t>
+        </is>
+      </c>
+      <c r="G70" s="6" t="inlineStr">
+        <is>
+          <t>DESIGN 4.6.2</t>
+        </is>
+      </c>
+      <c r="H70" s="6" t="inlineStr">
+        <is>
+          <t>Claude (proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="6" t="n"/>

--- a/docs/SCOPE_MOSCOW.xlsx
+++ b/docs/SCOPE_MOSCOW.xlsx
@@ -3566,7 +3566,7 @@
       </c>
       <c r="F70" s="6" t="inlineStr">
         <is>
-          <t>A per-glyph atlas can't join or reorder letters; needs a shaping step. Kept so it isn't forgotten</t>
+          <t>A per-glyph atlas can't join, reorder or stack letters. If ever needed: let Windows shape whole strings (its text system does this for every script) and draw the result, rather than drawing our own glyphs (owner and Claude: our own bitmap letters would be reinventing the wheel, and fonts are the player's installed ones)</t>
         </is>
       </c>
       <c r="G70" s="6" t="inlineStr">

--- a/docs/SCOPE_MOSCOW.xlsx
+++ b/docs/SCOPE_MOSCOW.xlsx
@@ -2978,7 +2978,7 @@
       </c>
       <c r="F56" s="6" t="inlineStr">
         <is>
-          <t>D62: back burner until a nicer way. FacetShape::terrace is built but off (it softens one-cell edits)</t>
+          <t>D62: back burner until a nicer way. Lead (docs/research/SURFACE_NETS.md, Gibson 1998): draw unedited ground at the terrain's continuous height clamped into each cell's cube: seam-safe, no iterations, edits pinned crisp</t>
         </is>
       </c>
       <c r="G56" s="6" t="inlineStr">

--- a/docs/SCOPE_MOSCOW.xlsx
+++ b/docs/SCOPE_MOSCOW.xlsx
@@ -3581,14 +3581,46 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="6" t="n"/>
-      <c r="B71" s="6" t="n"/>
-      <c r="C71" s="6" t="n"/>
-      <c r="D71" s="6" t="n"/>
-      <c r="E71" s="6" t="n"/>
-      <c r="F71" s="6" t="n"/>
-      <c r="G71" s="6" t="n"/>
-      <c r="H71" s="6" t="n"/>
+      <c r="A71" s="6" t="inlineStr">
+        <is>
+          <t>W070</t>
+        </is>
+      </c>
+      <c r="B71" s="6" t="inlineStr">
+        <is>
+          <t>Platform</t>
+        </is>
+      </c>
+      <c r="C71" s="6" t="inlineStr">
+        <is>
+          <t>Durable saves: flush the new file to disk before swapping it in, load the .bak when the main save is missing or damaged, and test every interruption point</t>
+        </is>
+      </c>
+      <c r="D71" s="6" t="inlineStr">
+        <is>
+          <t>Could</t>
+        </is>
+      </c>
+      <c r="E71" s="6" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="F71" s="6" t="inlineStr">
+        <is>
+          <t>From Grok/ChatGPT E15 (docs/grok_reviews/round2_E_part2.md): today safe against a game crash, not a power cut, and LoadGame never tries the .bak</t>
+        </is>
+      </c>
+      <c r="G71" s="6" t="inlineStr">
+        <is>
+          <t>DESIGN 7.3</t>
+        </is>
+      </c>
+      <c r="H71" s="6" t="inlineStr">
+        <is>
+          <t>Claude (proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="6" t="n"/>
